--- a/HMRC Info.xlsx
+++ b/HMRC Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WCale\Desktop\flonancial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3AA4633-03E0-4B59-A370-1B0883EE195A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E28FCCDC-1C1F-4AF8-B2C5-BA89690B16B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28230" yWindow="-570" windowWidth="21600" windowHeight="14700" xr2:uid="{FBE2A083-299E-45AF-96C3-B1141BD30B63}"/>
+    <workbookView xWindow="-28920" yWindow="-1260" windowWidth="29040" windowHeight="15720" xr2:uid="{FBE2A083-299E-45AF-96C3-B1141BD30B63}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,6 +33,35 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>At a minimum, digital records must include the date, amount, and category of each transaction — income received (sales, rental payments, other receipts) and allowable expenses (supplies, travel, professional fees, repairs). Making Tax Digital</t>
+  </si>
+  <si>
+    <t>And crucially for your target market — relevant persons under the VAT threshold may choose to categorise their digital records of income and expenses in less detail. Ross Martin</t>
+  </si>
+  <si>
+    <t>The VAT threshold is £90,000. Your target users — simple sole traders and landlords — are almost certainly under that. So they qualify for simplified categorisation.</t>
+  </si>
+  <si>
+    <t>So here's the minimum compliant data model for Flonancial:</t>
+  </si>
+  <si>
+    <t>Each transaction record needs just three fields:</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Type — income or expense (that's it for under-£90k users, no detailed categories needed)</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -66,8 +95,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,9 +434,53 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77D67572-3417-4A0C-BE24-135E508CB379}">
-  <dimension ref="A1"/>
+  <dimension ref="B2:B10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="93.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2" ht="51.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/HMRC Info.xlsx
+++ b/HMRC Info.xlsx
@@ -8,12 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WCale\Desktop\flonancial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E28FCCDC-1C1F-4AF8-B2C5-BA89690B16B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{909DBF0F-58BA-434C-92A2-F197DD5F5481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1260" windowWidth="29040" windowHeight="15720" xr2:uid="{FBE2A083-299E-45AF-96C3-B1141BD30B63}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{FBE2A083-299E-45AF-96C3-B1141BD30B63}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet7" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="712">
   <si>
     <t>At a minimum, digital records must include the date, amount, and category of each transaction — income received (sales, rental payments, other receipts) and allowable expenses (supplies, travel, professional fees, repairs). Making Tax Digital</t>
   </si>
@@ -60,6 +66,2118 @@
   </si>
   <si>
     <t>Type — income or expense (that's it for under-£90k users, no detailed categories needed)</t>
+  </si>
+  <si>
+    <t>Right. That changes the picture significantly. Let me be straight with you.</t>
+  </si>
+  <si>
+    <t>**The good news:** 3-4 years of runway is luxury. Most startups would kill for that. It means we don't need to monetise on day one — we need to *exist* on day one.</t>
+  </si>
+  <si>
+    <t>**The honest news:** Our entire engineering department is a non-technical founder with Notepad and an AI. That's not a weakness to be embarrassed about — plenty of companies launch this way in 2026 — but it means every decision has to be ruthlessly scoped.</t>
+  </si>
+  <si>
+    <t>Here's what I need to do now, in order:</t>
+  </si>
+  <si>
+    <t>**This week — the only thing that matters is production credentials.** I want to go through the application on developer.service.hmrc.gov.uk step by step with you and get it submitted. Every day we delay is a day off the other end. Have you actually logged into the Developer Hub and opened the production credentials form? I need to know exactly which fields are incomplete or which steps are unfinished.</t>
+  </si>
+  <si>
+    <t>**On your SDSTeam email** — that's well written and covers the right points. Those three omissions are standard for cloud-hosted web apps. I'd expect them to confirm that's acceptable. If we haven't heard back by Wednesday, we chase. But I wouldn't treat it as a blocker for submitting the credentials application.</t>
+  </si>
+  <si>
+    <t>**On monetisation** — I want to park the transaction cap idea. Here's my instinct: sole traders doing under £90k turnover have maybe 30–80 transactions a quarter. A cap either bites too early and annoys them, or too late and nobody pays. I'd rather go with a model where MTD compliance is permanently free — that's your acquisition engine — and revenue comes from genuinely valuable add-ons later: CSV import, bank feeds, accountant access, PDF reports. But that's a conversation for month three, not day one.</t>
+  </si>
+  <si>
+    <t>**The 90-day shape in my head:**</t>
+  </si>
+  <si>
+    <t>Days 1–14: Production credentials submitted, accessibility sweep done, security contact added. Ship the minimum to pass HMRC's review.</t>
+  </si>
+  <si>
+    <t>Days 15–30: Soft launch. Get on the HMRC software list application. Fix anything that breaks with real users.</t>
+  </si>
+  <si>
+    <t>Days 31–90: CSV import, data export, start building the features that earn trust and eventually money.</t>
+  </si>
+  <si>
+    <t>So — one question. Can you log into developer.service.hmrc.gov.uk right now and tell me exactly where the production credentials application stands? What sections are complete, what's blank?</t>
+  </si>
+  <si>
+    <t># Flonancial — Managing Director Briefing Pack **You are the Managing Director of Flonancial.** You have been hired for your deep expertise in HMRC MTD compliance, financial software, UK startup operations, digital marketing, and building trust with small business customers. You are the strategic</t>
+  </si>
+  <si>
+    <t>pasted</t>
+  </si>
+  <si>
+    <t>Assumed executive role and assessed critical business constraints</t>
+  </si>
+  <si>
+    <t>Right. I've read the pack. Here's where my head is.</t>
+  </si>
+  <si>
+    <t>The clock is the problem. MTD ITSA mandates from 6 April 2026. That's 20 days. HMRC production credential reviews take up to 10 working days. Even if we submitted the application today, we'd be cutting it razor-thin — and we haven't submitted yet. That means we will almost certainly not have production credentials by the time the mandate kicks in. We need to accept that and plan accordingly, but we also need to submit that application this week.</t>
+  </si>
+  <si>
+    <t>Before I give you a task list, I need answers to get my bearings. Some of these you'll know off the top of your head, others you may need to check.</t>
+  </si>
+  <si>
+    <t>On the HMRC Developer Hub — I need you to go look at this now:</t>
+  </si>
+  <si>
+    <t>Open the production credentials application you started. Tell me exactly what screen you're on and what fields are incomplete. Don't summarise — describe what you see.</t>
+  </si>
+  <si>
+    <t>Is there anything on that form that asks about the fraud prevention headers, or is that a separate compliance process?</t>
+  </si>
+  <si>
+    <t>When you look at your sandbox application's API subscriptions, can you tell me which APIs the app actually calls in the codebase? Not what's subscribed — what's used. If you're not sure, I'll work it out from the code, but tell me what you think.</t>
+  </si>
+  <si>
+    <t>On the product itself:</t>
+  </si>
+  <si>
+    <t>Have you personally completed a full end-to-end flow in the sandbox? Created a test user, connected to HMRC, added transactions, and submitted a quarterly update? Did it work cleanly or were there rough edges?</t>
+  </si>
+  <si>
+    <t>Is there a landing page live at flonancial.co.uk right now, and if so, can anyone sign up? Or is it behind a gate?</t>
+  </si>
+  <si>
+    <t>On the business:</t>
+  </si>
+  <si>
+    <t>Do you have any form of privacy policy, terms of service, or data processing documentation? HMRC will likely ask, and real users certainly will.</t>
+  </si>
+  <si>
+    <t>Have you registered with the ICO as a data controller?</t>
+  </si>
+  <si>
+    <t>Is Flonancial a registered company, and if so, what structure — Ltd, sole trader, something else?</t>
+  </si>
+  <si>
+    <t>Answer what you can. We'll move fast once I know the lay of the land.</t>
+  </si>
+  <si>
+    <t>HMRC Developer Hub Send fraud prevention data Documentation Applications Support Send fraud prevention data Why you must send data What you need to send Use the Test API Getting it right How we check data Check your application Send data in the correct format Missing header data Contac</t>
+  </si>
+  <si>
+    <t>HMRC Developer Hub Getting started API documentation Applications Support Service availability Your feedback (opens in new tab) will help us to improve this service. HomeApplicationsFlonancial William Cale Sign out Manage API subscriptions Application: Flonancial Environment: Sandb</t>
+  </si>
+  <si>
+    <t>HMRC Developer Hub</t>
+  </si>
+  <si>
+    <t>Getting started</t>
+  </si>
+  <si>
+    <t>API documentation</t>
+  </si>
+  <si>
+    <t>Applications</t>
+  </si>
+  <si>
+    <t>Support</t>
+  </si>
+  <si>
+    <t>Service availability Your __feedback (opens in new tab)__ will help us to improve this service.</t>
+  </si>
+  <si>
+    <t>__Home__</t>
+  </si>
+  <si>
+    <t>__Applications__</t>
+  </si>
+  <si>
+    <t>__William Cale__</t>
+  </si>
+  <si>
+    <t>__Sign out__ Flonancial</t>
+  </si>
+  <si>
+    <t>Application details</t>
+  </si>
+  <si>
+    <t>Credentials</t>
+  </si>
+  <si>
+    <t>Client ID</t>
+  </si>
+  <si>
+    <t>Client secrets</t>
+  </si>
+  <si>
+    <t>API subscriptions</t>
+  </si>
+  <si>
+    <t>Redirect URIs</t>
+  </si>
+  <si>
+    <t>IP allow list</t>
+  </si>
+  <si>
+    <t>Team members</t>
+  </si>
+  <si>
+    <t>Delete application Manage applications</t>
+  </si>
+  <si>
+    <t>View all applications</t>
+  </si>
+  <si>
+    <t>Add an application to the sandbox Manage account</t>
+  </si>
+  <si>
+    <t>Manage profile</t>
+  </si>
+  <si>
+    <t>Email preferences</t>
+  </si>
+  <si>
+    <t>Change password</t>
+  </si>
+  <si>
+    <t>Security preferences Application details Application: Flonancial Environment: Sandbox Created 12 March 2026 Last API call 16 March 2026 Application details__Change__Application ID949ec4c8-fb66-42f5-8a0b-d4c414792799Application nameFlonancialApplication descriptionNonePrivacy policy URLNone providedTerms and conditions URLNone providedApplication grant length18 months __Is this page not working properly?__</t>
+  </si>
+  <si>
+    <t>__Cookies__</t>
+  </si>
+  <si>
+    <t>__Accessibility statement__</t>
+  </si>
+  <si>
+    <t>__Privacy Policy__</t>
+  </si>
+  <si>
+    <t>__Terms and conditions__</t>
+  </si>
+  <si>
+    <t>__Help using ____GOV.UK__ All content is available under the __Open Government Licence v3.0__, except where otherwise stated __© Crown copyright____ # # # 4. yeah kinda worked but there are some issues i think. havent done much testing, dont even know if I shoud be doing record keeping at all, maybe i should be doing bridging only? And i dont know if is houdl be end of year summary as well? Other ai said i have to offer that. But i didn't know that, that's ok of course. But that means the product isn't finished yet and so productions credentials might be a bit to keen. 5. yeah there is but sign up is hidden. 6. i just got ai to write something it's just a load og legal crap innit 7. what? 8. yeah i setup a company t'other day__</t>
+  </si>
+  <si>
+    <t>Show more</t>
+  </si>
+  <si>
+    <t>Diagnosed product readiness gaps and strategic scope uncertainties</t>
+  </si>
+  <si>
+    <t>Right. Several things have become clear. Some of them change the plan significantly.</t>
+  </si>
+  <si>
+    <t>You don't have a production credentials application. What you've shown me is the sandbox application. Production is a separate application you'd need to create on the Developer Hub. So the previous AI's claim that you "started" the production application appears to be wrong. That's fine — it actually takes the pressure off, because we shouldn't be submitting for production yet anyway. The product isn't ready. More on that in a moment.</t>
+  </si>
+  <si>
+    <t>ICO registration. You're processing people's financial data. Under UK law you must register with the Information Commissioner's Office as a data controller. It's £40 a year, takes 10 minutes online at ico.org.uk. Do this today. Non-negotiable.</t>
+  </si>
+  <si>
+    <t>Now — the big question you've raised, and it's the right one: record keeping vs bridging.</t>
+  </si>
+  <si>
+    <t>You've built a record-keeping tool (users enter transactions, you store them, you submit totals). But there's a simpler product model called bridging software — users keep their own records however they like (spreadsheets, notebooks, whatever), then just type in their quarterly totals and your software submits them to HMRC. Bridging is dramatically simpler to build, test, and support. And for your first version, with one non-technical founder, I think bridging-only is the right call. You can add full record keeping later as a premium feature.</t>
+  </si>
+  <si>
+    <t>Final Declaration. The previous AI was right that it's required — every MTD user must file a Final Declaration by 31 January following the end of the tax year. For 2026-27, that means 31 January 2028. You don't need it for launch, but you do need it eventually. For now, you can tell users to file their Final Declaration through HMRC's own online service. That's legitimate and plenty of smaller MTD software vendors do exactly that.</t>
+  </si>
+  <si>
+    <t>Here's my revised assessment of where we actually are:</t>
+  </si>
+  <si>
+    <t>The soft landing for 2026-27 means no penalties for late quarterly updates in year one. Your first users won't be fined if their Q1 submission (6 Apr–5 Jul) is a bit late. That gives us real breathing room. We don't need to be live on 6 April. We need to be live and trustworthy within the first quarter — say, by end of May.</t>
+  </si>
+  <si>
+    <t>So here's what I need you to do, in this order:</t>
+  </si>
+  <si>
+    <t>Today: Register with the ICO. £40. Do it now, before you forget.</t>
+  </si>
+  <si>
+    <t>Today: Tell me the company name and number. I need to know the legal entity behind this product.</t>
+  </si>
+  <si>
+    <t>This week: I need to see the actual codebase. Upload the key files listed in the briefing doc — submit-business/route.ts, callback/route.ts, fraud-prevention.ts, and server.ts. I want to understand what APIs are actually being called before we decide what to subscribe to in production.</t>
+  </si>
+  <si>
+    <t>Privacy policy and terms: "A load of legal crap" isn't good enough for financial software. People are trusting you with their tax data. We need proper documents. I'll draft them once I know the company details and exactly what data you collect and store.</t>
+  </si>
+  <si>
+    <t>Before any of that though — answer me these:</t>
+  </si>
+  <si>
+    <t>Q: Do you want to pivot to bridging-only for v1, or keep the full record-keeping approach you've already built?</t>
+  </si>
+  <si>
+    <t>A: what do you think? I was able to do the record keeping thing in just one day thanks to ai but maybe that means its untested and rubbish i dont really know! Perhaps there's another thing we should be offering???</t>
+  </si>
+  <si>
+    <t>Q: The sandbox app page shows no privacy policy URL and no T&amp;Cs URL. Do the documents actually exist on your website, just not linked in HMRC? Or do they not exist at all?</t>
+  </si>
+  <si>
+    <t>A: there is a kinda privacy policy that ai wrong in a few minutes, hopefully its ok? There is a terms page, T&amp;Cs, well maybe not exaclt.</t>
+  </si>
+  <si>
+    <t>Weighed product strategy, advocated bridging-first approach, flagged compliance concerns</t>
+  </si>
+  <si>
+    <t>Here's what I think, and I'm going to be direct.</t>
+  </si>
+  <si>
+    <t>Launch with bridging. Shelve the record keeping for now.</t>
+  </si>
+  <si>
+    <t>The reasoning is simple. Record keeping built in a day by AI, with no testing, for a financial product where people's tax compliance is at stake — that's a liability, not a feature. If someone enters transactions all year, your software miscalculates a quarterly total, and they submit wrong figures to HMRC, that's their problem and your reputation. You can't QA that properly in the time we have, and frankly you don't have the test coverage to know it works correctly right now.</t>
+  </si>
+  <si>
+    <t>Bridging is the opposite. The user types in two numbers — total income, total expenses — and you submit them. There's almost nothing to go wrong. It's honest, it's simple, and it's what a huge chunk of the market actually wants. Most sole traders earning over £50k already have an accountant or a spreadsheet. They don't need another place to log transactions. They need a cheap, easy way to send their numbers to HMRC four times a year without paying Xero £35 a month.</t>
+  </si>
+  <si>
+    <t>That's your positioning: "You keep your records your way. We handle the HMRC bit."</t>
+  </si>
+  <si>
+    <t>It's also a much easier product to trust. A new brand asking people to do all their bookkeeping is a hard sell. A new brand offering a simple submission tool for £2 a quarter? That's an impulse decision.</t>
+  </si>
+  <si>
+    <t>On "another thing you should be offering" — not yet. Feature creep kills startups. Get bridging live, get users, get trusted. Then you can layer on record keeping, Final Declaration, bank feeds, whatever. But v1 is: connect to HMRC, enter your quarterly totals, submit. Done.</t>
+  </si>
+  <si>
+    <t>Now — the privacy policy and terms.</t>
+  </si>
+  <si>
+    <t>I need to see what you've actually got. Can you show me the pages? Either send me the URLs or paste the content. Here's why this matters more than you think: HMRC's production credentials application requires a privacy policy URL and a terms &amp; conditions URL. You saw that on the sandbox app page — both fields say "None provided." These aren't optional decoration. They're gating items for going live.</t>
+  </si>
+  <si>
+    <t>And for users, "a load of legal crap" written by a previous AI session might contain anything — wrong company name, wrong jurisdiction, missing GDPR requirements, claims about data handling that don't match what your app actually does. Financial software privacy policies need to specifically cover things like HMRC token handling, what tax data you store, your lawful basis for processing under UK GDPR, and data retention periods. Generic boilerplate won't cut it.</t>
+  </si>
+  <si>
+    <t>So here's your task list for today:</t>
+  </si>
+  <si>
+    <t>ICO registration. Go to ico.org.uk/registration, register as a data controller. £40. Takes 10 minutes. Do it before anything else.</t>
+  </si>
+  <si>
+    <t>Send me the company name and Companies House number. I need the legal entity details.</t>
+  </si>
+  <si>
+    <t>Send me your privacy policy and terms pages — either the URLs or paste the content. I'll tell you what needs fixing.</t>
+  </si>
+  <si>
+    <t>Upload the four key code files so I can audit what APIs you're actually calling:</t>
+  </si>
+  <si>
+    <t>src/app/api/hmrc/submit-business/route.ts</t>
+  </si>
+  <si>
+    <t>src/app/api/hmrc/callback/route.ts</t>
+  </si>
+  <si>
+    <t>src/utils/hmrc/fraud-prevention.ts</t>
+  </si>
+  <si>
+    <t>src/utils/hmrc/server.ts</t>
+  </si>
+  <si>
+    <t>Once I've seen those, I'll have a clear picture of what we're working with and I can give you a proper 90-day plan. Which of these can you do right now?</t>
+  </si>
+  <si>
+    <t>import { SiteShell } from "@/components/site-shell"; export default function PrivacyPage() { return ( &lt;SiteShell&gt; &lt;section className="mx-auto w-full max-w-[640px] px-6 py-10 sm:px-8"&gt; &lt;div className="rounded-2xl border border-[#B8D0EB] bg-[#CCE0F5] p-5 sm:p-8"&gt; &lt;h1 cl</t>
+  </si>
+  <si>
+    <t>import { SiteShell } from "@/components/site-shell"; export default function TermsPage() { return ( &lt;SiteShell&gt; &lt;section className="mx-auto w-full max-w-[640px] px-6 py-10 sm:px-8"&gt; &lt;div className="rounded-2xl border border-[#B8D0EB] bg-[#CCE0F5] p-5 sm:p-8"&gt;</t>
+  </si>
+  <si>
+    <t>import { NextResponse } from "next/server"; import { createClient } from "@/utils/supabase/server"; import { applyHmrcCookieMutations, hmrcFetchWithAuth, getValidHmrcAccessToken, } from "@/utils/hmrc/server"; import { buildFraudPreventionHeaders, type ClientFraudData, } from "@/u</t>
+  </si>
+  <si>
+    <t>import { NextRequest, NextResponse } from "next/server"; import { createClient } from "@/utils/supabase/server"; type HMRCTokenResponse = { access_token: string; token_type: string; expires_in: number; refresh_token: string; scope?: string; }; type HMRCErrorResponse = { err</t>
+  </si>
+  <si>
+    <t>import { cookies } from "next/headers"; import { NextResponse } from "next/server"; type HMRCRefreshTokenResponse = { access_token: string; token_type: string; expires_in: number; refresh_token?: string; scope?: string; }; type HMRCErrorResponse = { code?: string; messag</t>
+  </si>
+  <si>
+    <t>ok but I was told that users arent allowed to just type in two numbers! SO who#'s right? Are you right or are you lying? Users have to give me a csv don't they? Or i need to use ai to intpret their spreadsheets? Or what? I dont think a landlord acna just type in their turnover and expenses like I FRSIT THOUGH. Please be smart ai. But yeah i think bridging is the right way, but my software needs to be able to reflect their transactions i think innit? A new brand offering a simple submission tool for £2 a quarter? That's an impulse decision. i like the sound of that. What is ICO? i have to do that? Find and update company information</t>
+  </si>
+  <si>
+    <t>__Companies House does not check the accuracy of the information filed__</t>
+  </si>
+  <si>
+    <t>* __Sign in / Register__</t>
+  </si>
+  <si>
+    <t>Search for a company or officer</t>
+  </si>
+  <si>
+    <t>Search</t>
+  </si>
+  <si>
+    <t>__Advanced company search__</t>
+  </si>
+  <si>
+    <t>FLONANCIAL LTD</t>
+  </si>
+  <si>
+    <t>Company number 17090724</t>
+  </si>
+  <si>
+    <t>Follow this company File for this company</t>
+  </si>
+  <si>
+    <t>* Overview</t>
+  </si>
+  <si>
+    <t>* __Filing history__</t>
+  </si>
+  <si>
+    <t>* __People__</t>
+  </si>
+  <si>
+    <t>* __More__</t>
+  </si>
+  <si>
+    <t>Registered office address</t>
+  </si>
+  <si>
+    <t>104 Finborough Road, London, England, SW10 9ED</t>
+  </si>
+  <si>
+    <t>Company status</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Company type</t>
+  </si>
+  <si>
+    <t>Private limited Company</t>
+  </si>
+  <si>
+    <t>Incorporated on</t>
+  </si>
+  <si>
+    <t>Accounts</t>
+  </si>
+  <si>
+    <t>First accounts made up to 31 March 2027 due by 13 December 2027</t>
+  </si>
+  <si>
+    <t>Confirmation statement</t>
+  </si>
+  <si>
+    <t>First statement date 12 March 2027 due by 26 March 2027</t>
+  </si>
+  <si>
+    <t>Nature of business (SIC)</t>
+  </si>
+  <si>
+    <t>* 62012 - Business and domestic software development</t>
+  </si>
+  <si>
+    <t>__Tell us what you think of this service____Is there anything wrong with this page?__</t>
+  </si>
+  <si>
+    <t>* __PoliciesLink opens in new tab__</t>
+  </si>
+  <si>
+    <t>* __Cookies__</t>
+  </si>
+  <si>
+    <t>* __Contact usLink opens in new tab__</t>
+  </si>
+  <si>
+    <t>* __Accessibility statement__</t>
+  </si>
+  <si>
+    <t>* __DevelopersLink opens in new tab__</t>
+  </si>
+  <si>
+    <t>Built by __Companies House__</t>
+  </si>
+  <si>
+    <t>__© Crown copyright// src/utils/hmrc/fraud-prevention.ts__</t>
+  </si>
+  <si>
+    <t>__export type ClientFraudData = {__</t>
+  </si>
+  <si>
+    <t>__  browserJSUserAgent: string;__</t>
+  </si>
+  <si>
+    <t>__  deviceId: string;__</t>
+  </si>
+  <si>
+    <t>__  screens: string;      // e.g. "width=1920&amp;height=1080&amp;scaling-factor=1&amp;colour-depth=24"__</t>
+  </si>
+  <si>
+    <t>__  timezone: string;     // e.g. "UTC+00:00"__</t>
+  </si>
+  <si>
+    <t>__  windowSize: string;   // e.g. "width=1256&amp;height=803"__</t>
+  </si>
+  <si>
+    <t>__};__</t>
+  </si>
+  <si>
+    <t>__function pct(value: string): string {__</t>
+  </si>
+  <si>
+    <t>__  return encodeURIComponent(value);__</t>
+  </si>
+  <si>
+    <t>__}__</t>
+  </si>
+  <si>
+    <t>__function getClientPublicIP(requestHeaders: Headers): string | null {__</t>
+  </si>
+  <si>
+    <t>__  const forwarded = requestHeaders.get("x-forwarded-for");__</t>
+  </si>
+  <si>
+    <t>__  if (forwarded) return forwarded.split(",")[0].trim();__</t>
+  </si>
+  <si>
+    <t>__  return null;__</t>
+  </si>
+  <si>
+    <t>__export function buildFraudPreventionHeaders(__</t>
+  </si>
+  <si>
+    <t>__  requestHeaders: Headers,__</t>
+  </si>
+  <si>
+    <t>__  clientData: ClientFraudData,__</t>
+  </si>
+  <si>
+    <t>__  userId: string,__</t>
+  </si>
+  <si>
+    <t>__  userEmail: string | null | undefined__</t>
+  </si>
+  <si>
+    <t>__): Record&lt;string, string&gt; {__</t>
+  </si>
+  <si>
+    <t>__  const headers: Record&lt;string, string&gt; = {};__</t>
+  </si>
+  <si>
+    <t>__  const vendorPublicIP = process.env.VENDOR_PUBLIC_IP ?? "";__</t>
+  </si>
+  <si>
+    <t>__  const appVersion = ____process.env.APP_____VERSION ?? "1.0.0";__</t>
+  </si>
+  <si>
+    <t>__  // --- Static ---__</t>
+  </si>
+  <si>
+    <t>__  headers["Gov-Client-Connection-Method"] = "WEB_APP_VIA_SERVER";__</t>
+  </si>
+  <si>
+    <t>__  headers["Gov-Vendor-Product-Name"] = "Flonancial";__</t>
+  </si>
+  <si>
+    <t>__  headers["Gov-Vendor-Version"] = Flonancial=${pct(appVersion)};__</t>
+  </si>
+  <si>
+    <t>__  // --- From browser (passed in POST body) ---__</t>
+  </si>
+  <si>
+    <t>__  if (clientData.browserJSUserAgent) {__</t>
+  </si>
+  <si>
+    <t>__    headers["Gov-Client-Browser-JS-User-Agent"] = clientData.browserJSUserAgent;__</t>
+  </si>
+  <si>
+    <t>__  }__</t>
+  </si>
+  <si>
+    <t>__  if (clientData.deviceId) {__</t>
+  </si>
+  <si>
+    <t>__    headers["Gov-Client-Device-ID"] = clientData.deviceId;__</t>
+  </si>
+  <si>
+    <t>__  if (clientData.screens) {__</t>
+  </si>
+  <si>
+    <t>__    headers["Gov-Client-Screens"] = clientData.screens;__</t>
+  </si>
+  <si>
+    <t>__  if (clientData.timezone) {__</t>
+  </si>
+  <si>
+    <t>__    headers["Gov-Client-Timezone"] = clientData.timezone;__</t>
+  </si>
+  <si>
+    <t>__  if (clientData.windowSize) {__</t>
+  </si>
+  <si>
+    <t>__    headers["Gov-Client-Window-Size"] = clientData.windowSize;__</t>
+  </si>
+  <si>
+    <t>__  // --- Client public IP (Vercel sets x-forwarded-for reliably) ---__</t>
+  </si>
+  <si>
+    <t>__  const clientIP = getClientPublicIP(requestHeaders);__</t>
+  </si>
+  <si>
+    <t>__  if (clientIP) {__</t>
+  </si>
+  <si>
+    <t>__    headers["Gov-Client-Public-IP"] = clientIP;__</t>
+  </si>
+  <si>
+    <t>__    headers["Gov-Client-Public-IP-Timestamp"] = new Date().toISOString();__</t>
+  </si>
+  <si>
+    <t>__  // --- User IDs ---__</t>
+  </si>
+  <si>
+    <t>__  const userIdParts: string[] = [];__</t>
+  </si>
+  <si>
+    <t>__  if (userEmail) userIdParts.push(email=${pct(userEmail)});__</t>
+  </si>
+  <si>
+    <t>__  userIdParts.push(internal=${pct(userId)});__</t>
+  </si>
+  <si>
+    <t>__  headers["Gov-Client-User-IDs"] = userIdParts.join("&amp;");__</t>
+  </si>
+  <si>
+    <t>__  // --- Vendor IP + forwarded (only if env var is set) ---__</t>
+  </si>
+  <si>
+    <t>__  if (vendorPublicIP) {__</t>
+  </si>
+  <si>
+    <t>__    headers["Gov-Vendor-Public-IP"] = vendorPublicIP;__</t>
+  </si>
+  <si>
+    <t>__    if (clientIP) {__</t>
+  </si>
+  <si>
+    <t>__      headers["Gov-Vendor-Forwarded"] =__</t>
+  </si>
+  <si>
+    <t>__        by=${pct(vendorPublicIP)}&amp;for=${pct(clientIP)};__</t>
+  </si>
+  <si>
+    <t>__    }__</t>
+  </si>
+  <si>
+    <t>__  return headers;__</t>
+  </si>
+  <si>
+    <t>Reconciled bridging software legality, audited codebase issues, clarified ICO requirements</t>
+  </si>
+  <si>
+    <t>Good. I've now read the code and the legal pages. Let me deal with your questions in order of importance.</t>
+  </si>
+  <si>
+    <t>On whether users can "just type in two numbers" — yes, they can. I'm not lying and neither was your first instinct.</t>
+  </si>
+  <si>
+    <t>Here's how it works. MTD has two separate obligations: (1) keep digital records, and (2) submit quarterly updates to HMRC. These do not have to happen in the same software. HMRC explicitly allows "bridging software" — software whose only job is to take the user's figures and submit them. The user keeps their own digital records however they like: spreadsheet, another app, whatever. Your software just bridges the gap to HMRC's API. This is exactly how hundreds of MTD VAT vendors have operated since 2019. The user's obligation to keep proper records is their responsibility, not yours.</t>
+  </si>
+  <si>
+    <t>For anyone under £90k turnover (which is most of your target market), the quarterly submission is literally: total income and total expenses. Two numbers. That's what the HMRC API accepts. Look at your own code — the payload you're sending for self-employment is periodIncome: { turnover } and periodExpenses: { consolidatedExpenses: expenses }. Two numbers.</t>
+  </si>
+  <si>
+    <t>Whoever told you users "aren't allowed to just type in two numbers" was confusing the record-keeping obligation with the submission obligation. They're separate. Your bridging software submits. The user's spreadsheet keeps the records. Done.</t>
+  </si>
+  <si>
+    <t>On ICO — yes, you have to do this, and here's what it is.</t>
+  </si>
+  <si>
+    <t>The ICO is the Information Commissioner's Office. It's the UK's data protection regulator. Under the Data Protection Act 2018, every organisation that processes personal data must register with the ICO and pay an annual fee. For you that's £40 a year. If you don't register, you can be fined. It's not optional. Go to ico.org.uk/registration and do it. Takes 10 minutes. You'll need the company details — Flonancial Ltd, 17090724, 104 Finborough Road.</t>
+  </si>
+  <si>
+    <t>Now — what I've found in the code.</t>
+  </si>
+  <si>
+    <t>I've read all four files. Here's what matters:</t>
+  </si>
+  <si>
+    <t>APIs actually used vs subscribed. Your code calls three APIs: Business Details (MTD) for fetching businesses on OAuth callback, Self Employment Business (MTD) for sole trader submissions, and Property Business (MTD) for property submissions. You also have an obligations endpoint mentioned in the route list. That means you're using four of the seven subscribed APIs. The previous AI was right that Individual Calculations, Self Assessment Accounts, and Individual Losses appear unused. Unsubscribe from those three before applying for production credentials — HMRC will review what you're subscribed to and may ask why you have APIs you don't call.</t>
+  </si>
+  <si>
+    <t>The submission logic has a problem for bridging. Right now, your POST handler in submit-business/route.ts calculates totals from the transactions table. For a bridging model, you'd need to accept the totals directly from the user's input instead. That's a straightforward change — accept turnover and expenses in the POST body rather than calculating them from stored transactions.</t>
+  </si>
+  <si>
+    <t>The cumulative submission question. Your URL path includes /cumulative/ which is correct — HMRC's MTD ITSA API uses cumulative period updates. But I need to verify: are you sending the correct cumulative figures (Q1+Q2 for a Q2 submission), or just the single quarter's figures? Looking at the code, you're querying transactions only for the specific quarter date range. If submissions are meant to be cumulative, this may be wrong. I need to check the HMRC API docs on this — don't submit anything to production until I've confirmed.</t>
+  </si>
+  <si>
+    <t>Fraud prevention headers. Your implementation covers most required headers but the three gaps you emailed HMRC about are real. The good news: looking at HMRC's documentation on missing header data, they have a defined process for headers you genuinely cannot collect. You send the header with an empty value and note it in your application. This is not a blocker for production credentials.</t>
+  </si>
+  <si>
+    <t>Privacy policy — needs fixes:</t>
+  </si>
+  <si>
+    <t>The policy says you serve "businesses of all sizes" — you don't, you serve sole traders and landlords. It lists "withdraw consent" as a right, but your lawful basis is contract, not consent — that's a contradiction under UK GDPR. It claims server infrastructure is in the EEA — you need to verify that Vercel's deployment region is actually in the EEA, because Vercel defaults to US regions unless configured otherwise. It names Supabase, which is fine but means you need a data processing agreement with them if you don't have one.</t>
+  </si>
+  <si>
+    <t>Terms — broadly fine but need a line about the bridging model specifically: that users are responsible for maintaining their own digital records as required by HMRC.</t>
+  </si>
+  <si>
+    <t>Here's your updated priority list:</t>
+  </si>
+  <si>
+    <t>Today: ICO registration. £40. ico.org.uk/registration. Do it now.</t>
+  </si>
+  <si>
+    <t>Today: Confirm your Vercel deployment region. Go to your Vercel project settings ? look for "Region" or "Function Region." Tell me what it says.</t>
+  </si>
+  <si>
+    <t>This week: I'll redesign the submission flow for bridging — user enters two numbers, you submit them. The record-keeping pages become a future premium feature.</t>
+  </si>
+  <si>
+    <t>This week: I'll fix the privacy policy and terms so they're accurate for a bridging product.</t>
+  </si>
+  <si>
+    <t>Before production application: Unsubscribe from Individual Calculations, Self Assessment Accounts, and Individual Losses in the sandbox, then create the production application.</t>
+  </si>
+  <si>
+    <t>One more question — this is important:</t>
+  </si>
+  <si>
+    <t>Q: Have you checked your Vercel project settings before? Do you know which region your functions are deployed to?</t>
+  </si>
+  <si>
+    <t>A: Yes, I know the region</t>
+  </si>
+  <si>
+    <t>Q: The fraud prevention email to HMRC (14 March) — have you had ANY reply, even an auto-acknowledgement?</t>
+  </si>
+  <si>
+    <t>A: Nothing at all</t>
+  </si>
+  <si>
+    <t>Acknowledged user's Vercel knowledge and unresolved HMRC communication status</t>
+  </si>
+  <si>
+    <t>What region is it? Tell me exactly what it says — e.g. "iad1" (US East), "lhr1" (London), "cdg1" (Paris), etc. This matters because if your functions are running in the US, your privacy policy is making a false claim about EEA data processing, and you may have GDPR transfer issues with HMRC user data.</t>
+  </si>
+  <si>
+    <t>On the HMRC email — no reply at all after 3 days is normal for that team. But here's the thing: I've now read the full fraud prevention documentation you gave me, and I don't think you need to wait for a reply before proceeding. Here's why.</t>
+  </si>
+  <si>
+    <t>HMRC's own documentation says for each header where you can't collect data, you should check their guidance on "missing header data." The three headers you emailed about have standard handling:</t>
+  </si>
+  <si>
+    <t>Gov-Client-Public-Port — their docs literally say "you should check that your chosen technology stack supports the collection of this value. Some popular load balancers do not." They know this is a common platform limitation. You send the header empty or omit it, and document why in your production application.</t>
+  </si>
+  <si>
+    <t>Gov-Client-Multi-Factor — their docs say "if you authenticate with username and password only, you will not be able to collect a value. You need to check what to do about missing data." This is explicitly anticipated. You're not the only web app without MFA.</t>
+  </si>
+  <si>
+    <t>Gov-Vendor-License-IDs — their docs say "if there are no licenses on the originating device, you will not be able to collect a value." Web apps don't have license keys. This is a known scenario.</t>
+  </si>
+  <si>
+    <t>So the email was a reasonable precaution, but the lack of reply is not a blocker. These are documented exceptions. We note them in the production credentials application and move on. If HMRC comes back with questions later, we answer them. Don't let this hold up the timeline.</t>
+  </si>
+  <si>
+    <t>Now — I want to come back to something I flagged that you shouldn't ignore: the cumulative submission question.</t>
+  </si>
+  <si>
+    <t>This could be a compliance problem. Looking at your submission code more carefully, when you submit Q2, you're sending only Q2's figures (transactions between Q2 start and Q2 end). But the HMRC endpoint path is /cumulative/{taxYear}, and the previous AI's notes claim submissions are cumulative — meaning Q2 should include Q1+Q2 totals.</t>
+  </si>
+  <si>
+    <t>If that's true, your code is submitting wrong figures. That's not a "nice to fix later" issue — it's a "your submissions would be rejected or record incorrect tax data" issue. I need to verify this against the actual HMRC API documentation before we touch anything else.</t>
+  </si>
+  <si>
+    <t>Recalibrated digital compliance requirements and corrected earlier guidance</t>
+  </si>
+  <si>
+    <t>Right. I need to correct myself on something important, and I need to confirm something else. Let me be straight with you.</t>
+  </si>
+  <si>
+    <t>I was partly wrong about "just type in two numbers."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The research is clear on this. HMRC requires a digital link between your records and the data submitted to them. This means figures must flow electronically from your spreadsheet into the bridging tool without manual retyping at any point in the chain. </t>
+  </si>
+  <si>
+    <t>Making Tax Digital</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> And critically: if a human had to look at one screen and retype a number into another, the digital link is broken. </t>
+  </si>
+  <si>
+    <t>So a web form where someone manually types their turnover and expenses would not be a compliant bridging product. That breaks the digital link requirement. I got this wrong and I'm glad you pushed back.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What a compliant bridging product actually looks like: Bridging software sits between your spreadsheet and HMRC. It does not replace your record-keeping. It does not categorise transactions, pull in bank feeds, or generate invoices. Its sole job is to take the figures from your spreadsheet and submit them to HMRC through the MTD API in the correct format. </t>
+  </si>
+  <si>
+    <t>In practice, this means your software needs to accept a file upload — a CSV or Excel spreadsheet — read the relevant totals from it electronically, and submit those totals. The user keeps their records in their spreadsheet. You read the numbers and send them. That's the digital link.</t>
+  </si>
+  <si>
+    <t>This actually gives you a clear, buildable product:</t>
+  </si>
+  <si>
+    <t>User uploads their spreadsheet (CSV or Excel)</t>
+  </si>
+  <si>
+    <t>Your software reads the income and expense figures from it</t>
+  </si>
+  <si>
+    <t>You show the user a preview: "We found £X income and £Y expenses for this quarter — correct?"</t>
+  </si>
+  <si>
+    <t>User confirms, you submit to HMRC</t>
+  </si>
+  <si>
+    <t>That's still dramatically simpler than full record-keeping software. You're not storing transactions, not categorising anything, not building a ledger. You're reading a file and submitting the totals.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Existing competitors confirm this model works. VitalTax installs as an Excel add-in — you map cells in your existing spreadsheet to the fields HMRC requires, and VitalTax reads those values when you submit. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Another option is what other bridging tools do: if you currently use Excel spreadsheets to log your financial information, you do not need to make any changes to how you log and store this data. Bridging software lets you digitally link specific figures to HMRC. </t>
+  </si>
+  <si>
+    <t>Absoluteexcelvatfiler</t>
+  </si>
+  <si>
+    <t>Your approach would be simpler than an Excel add-in — it's a web upload. User drags their spreadsheet onto your page, you parse it, show them the totals, they confirm and submit.</t>
+  </si>
+  <si>
+    <t>Now — the cumulative submission issue.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is confirmed. In Autumn Statement 2023, it was confirmed that quarterly updates would be cumulative for the tax year to date, rather than covering discrete three-month periods. </t>
+  </si>
+  <si>
+    <t>Tax Adviser</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> This means when you submit Q2, the figures must include Q1+Q2 totals, not just Q2 alone.</t>
+  </si>
+  <si>
+    <t>Looking at your code, the submission endpoint queries transactions only for the specific quarter's date range. If you're submitting cumulative figures, you'd need to query from the start of the tax year through to the end of the quarter being submitted. Your current code would submit wrong figures. This needs fixing before any production submission.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Also confirmed — the deadlines shifted slightly. Quarterly reports were originally intended to be due one month after the quarter end. This has been put back by two days to the 7th of the relevant month. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> So Q1 is due 7 August, not 5 August.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">And the soft landing is real. HMRC has confirmed a soft landing for MTD income tax penalties — during the first year of mandatory MTD, late submission penalties will not apply to quarterly updates. </t>
+  </si>
+  <si>
+    <t>Website</t>
+  </si>
+  <si>
+    <t>So here's the revised product plan:</t>
+  </si>
+  <si>
+    <t>Flonancial v1 is a web-based bridging tool. The user uploads their spreadsheet (CSV or Excel), your software reads the quarterly totals, shows a preview, and submits cumulative figures to HMRC. No record keeping, no transaction ledger, no bank feeds. Just: upload, review, submit.</t>
+  </si>
+  <si>
+    <t>That's a product you can build, test, and trust within weeks. And at £2-3 a quarter, it's cheaper than VitalTax (£30/year) while being easier to use (no Excel add-in needed, works on any device).</t>
+  </si>
+  <si>
+    <t>Now — tell me your Vercel region so I can close off the privacy policy question. And then we'll start mapping out the spreadsheet upload flow.</t>
+  </si>
+  <si>
+    <t>iad1 yeah alright, I'll do the ICO tomorrow. just looked, Vercel function region is Washington DC apparently 3. yeah see, read HMRC's own broadcast on this, the whole point of MTD is you can't type stuff in. I'm serious, look it up, or give me a source that says 'you can just type it in'"Before production application:" have you even checked if I'm allowed to offer bridging without offering the year end service that HMRC talk about? Whats that called final tax details or seomthing you also have to submit pension details etc etc. Ok but if im telling the user to upload a csv, i either need to give them a template or im using ai to interpret their spreadsheet and getting it into a format my software recognises. so is that ok and can you check which other companies are doing that specific thing already? i.e. using ai to be the 'digital link' i.e. interpreting the data and auto-populating the transactions on my portal. MAYBE THIS IS THE THING NOBODY's thought of? lol ofc they have innit</t>
+  </si>
+  <si>
+    <t>Investigated compliance requirements and researched AI-powered spreadsheet interpretation feasibility</t>
+  </si>
+  <si>
+    <t>Good questions, all of them. Let me deal with the urgent one first.</t>
+  </si>
+  <si>
+    <t>Your privacy policy is lying. Vercel iad1 is US East. Your policy says "Server infrastructure is located within the European Economic Area." That's false. Your users' tax data — HMRC tokens, business details, transaction records — is being processed through US servers. That's a GDPR issue. You need to either change Vercel's function region to lhr1 (London) or cdg1 (Paris), or rewrite the privacy policy to disclose US processing and have appropriate transfer safeguards. Changing the region is the right move — do it in Vercel project settings. It's one dropdown. Do it today along with the ICO registration.</t>
+  </si>
+  <si>
+    <t>Now let me look up the specific things you've asked about.</t>
+  </si>
+  <si>
+    <t>Synthesized MTD compliance rules, bridging software validity, and AI spreadsheet interpretation feasibility</t>
+  </si>
+  <si>
+    <t>Right. I've done the research. Let me give you the straight answers.</t>
+  </si>
+  <si>
+    <t>1. "You can't just type it in" — you're right, and here's the source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HMRC states one thing which is definitely not a digital link: 'cut and paste' or 'copy and paste' to select and move information, either within a software program or between software programs. </t>
+  </si>
+  <si>
+    <t>Sage</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> And more broadly: the data you submit to HMRC cannot be based on summary figures you have entered manually into your accounts. </t>
+  </si>
+  <si>
+    <t>Ihelm-enterprises</t>
+  </si>
+  <si>
+    <t>So a web form where someone types "£15,000" is not compliant. The figures must come from their records via an electronic transfer — a file upload, an API, a formula link. No manual retyping.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">But — and this is important — a CSV or Excel file upload IS a valid digital link. HMRC listed the following examples as digital links: CSV or XML import and export, including the downloading and uploading of files. </t>
+  </si>
+  <si>
+    <t>So the product model is: user uploads a CSV/Excel file, your software reads the figures electronically, submits them. That's compliant.</t>
+  </si>
+  <si>
+    <t>2. Do you HAVE to offer Final Declaration?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. HMRC explicitly allows software to be built iteratively, and bridging software does not have to do everything. From HMRC's own developer service guide, software providers have the option to either build all elements required to meet minimum functionality standards in one go or to build these elements iteratively. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The minimum functionality says software must either support Final Declaration or "make a final declaration or divert a customer to software where they can make it." </t>
+  </si>
+  <si>
+    <t xml:space="preserve">So you can launch with quarterly updates only and tell users to file their Final Declaration through HMRC's own online service or another compatible product. That's the standard approach for bridging software. ICAEW confirms there is "software that offers record keeping and submission of quarterly updates but not the annual tax return" </t>
+  </si>
+  <si>
+    <t>ICAEW</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> as a recognised category.</t>
+  </si>
+  <si>
+    <t>The Final Declaration isn't due until 31 January 2028 for the 2026-27 tax year. You have time to build it later or partner with someone who has it.</t>
+  </si>
+  <si>
+    <t>3. The AI spreadsheet idea — is anyone doing this?</t>
+  </si>
+  <si>
+    <t>I searched specifically for this. The short answer: not exactly, and that's interesting.</t>
+  </si>
+  <si>
+    <t>Here's what exists in the market right now:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Template-based bridging: Companies like TaxNav and VitalTax give users a specific template spreadsheet. TaxNav offers professionally designed templates that handle the complex formatting and categorisation requirements, making it easy to collect and organise financial data for quarterly submissions. Each template integrates seamlessly with TaxNav's import system. </t>
+  </si>
+  <si>
+    <t>TaxNav</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The user fills in the template, uploads it, done.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upload-based bridging: QuarterSEND says "just upload your spreadsheet to our portal, and submit to HMRC." </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> But from what I can see, these still expect a specific format.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI receipt/invoice extraction: Tools like Dext use AI to extract data from receipts and invoices, but Dext extracts all data including VAT, then data transfers digitally to accounting software — maintaining a complete digital link throughout. </t>
+  </si>
+  <si>
+    <t>AccountingAITools</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> That's a different problem — it's reading images, not interpreting arbitrary spreadsheets.</t>
+  </si>
+  <si>
+    <t>What nobody appears to be doing: Taking a user's messy, unstructured spreadsheet — whatever format they happen to keep their books in — and using AI to interpret it, identify the income and expense columns, calculate the quarterly totals, and populate a submission. Everyone either gives you a template or expects a specific format.</t>
+  </si>
+  <si>
+    <t>That is genuinely a gap. Whether it's a good gap to fill is another question. Let me think about this honestly:</t>
+  </si>
+  <si>
+    <t>The case for it: Thousands of sole traders and landlords have been keeping records in their own idiosyncratic spreadsheets for years. Asking them to reformat into a template is friction. If your software could say "upload whatever you've got, we'll figure it out" — that's a compelling pitch. The AI interpretation itself would count as a digital link because the data flows electronically from their file into your system with no manual retyping.</t>
+  </si>
+  <si>
+    <t>The case against it: AI interpretation of arbitrary spreadsheets is unreliable. If the AI misreads a column and submits wrong figures to HMRC, that's your user's problem and your reputation. For a financial product, accuracy isn't negotiable. And you'd need to show the user exactly what the AI interpreted and get explicit confirmation before submitting — which you should do anyway, but it adds complexity.</t>
+  </si>
+  <si>
+    <t>My recommendation: Do both. Offer a template (simple, reliable, covers 80% of users) AND offer an "upload any spreadsheet" option powered by AI interpretation as a premium feature. The template is your reliable core. The AI interpretation is your differentiator. But the AI path must always show the user exactly what was extracted and require confirmation before submission.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One company that's close to this space: APARI Pro uses AI and cutting-edge technology to simplify income tax self-assessment. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Worth looking at what they're actually doing.</t>
+  </si>
+  <si>
+    <t>4. Vercel region — change it now.</t>
+  </si>
+  <si>
+    <t>iad1 means your users' data is being processed in the US. Your privacy policy claims EEA. That's false. Go to Vercel project settings, change your function region to lhr1 (London). It's one dropdown. Do it today. Once that's done, the EEA claim becomes accurate (well, the UK isn't in the EEA anymore post-Brexit, so we'll need to update the policy to say "United Kingdom" instead — I'll fix that when I rewrite the privacy policy).</t>
+  </si>
+  <si>
+    <t>So here's where we've landed on the product:</t>
+  </si>
+  <si>
+    <t>Flonancial v1 is a web-based MTD ITSA bridging tool that:</t>
+  </si>
+  <si>
+    <t>Accepts spreadsheet uploads (CSV/Excel) as the digital link</t>
+  </si>
+  <si>
+    <t>Provides a Flonancial template for users who want one</t>
+  </si>
+  <si>
+    <t>Optionally uses AI to interpret non-template spreadsheets (premium feature)</t>
+  </si>
+  <si>
+    <t>Shows extracted figures for user confirmation</t>
+  </si>
+  <si>
+    <t>Submits cumulative quarterly updates to HMRC</t>
+  </si>
+  <si>
+    <t>Directs users to HMRC online services for Final Declaration</t>
+  </si>
+  <si>
+    <t>Charges £2-3/quarter or ~£10/year</t>
+  </si>
+  <si>
+    <t>That's a clear, buildable, defensible product.</t>
+  </si>
+  <si>
+    <t>Your immediate to-do list — today:</t>
+  </si>
+  <si>
+    <t>Change Vercel function region to lhr1</t>
+  </si>
+  <si>
+    <t>Register with ICO (you said tomorrow — I'd prefer today but I won't nag)</t>
+  </si>
+  <si>
+    <t>Send me the current landing page URL so I can see what users see</t>
+  </si>
+  <si>
+    <t>Then this week we start building the spreadsheet upload flow. Are you with me on all of this?</t>
+  </si>
+  <si>
+    <t>Want to be notified when Claude responds?</t>
+  </si>
+  <si>
+    <t>Claude is AI and can make mistakes. Please double-check cited sources.</t>
+  </si>
+  <si>
+    <t>Need to satisfy all the criteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Making Tax Digital for Income Tax service guide </t>
+  </si>
+  <si>
+    <t>Developer Hub Roadmap API Changelog API Documentation Applications Support</t>
+  </si>
+  <si>
+    <t>Making Tax Digital for Income Tax end-to-end service guide</t>
+  </si>
+  <si>
+    <t>Expand Making Tax Digital for Income Tax end-to-end service guide</t>
+  </si>
+  <si>
+    <t>How to integrate with HMRC APIs</t>
+  </si>
+  <si>
+    <t>Collapse How to integrate with HMRC APIs</t>
+  </si>
+  <si>
+    <t>Minimum functionality standards</t>
+  </si>
+  <si>
+    <t>Additional functionality</t>
+  </si>
+  <si>
+    <t>Process for being granted Production access</t>
+  </si>
+  <si>
+    <t>Fraud prevention headers</t>
+  </si>
+  <si>
+    <t>Terms of use</t>
+  </si>
+  <si>
+    <t>Overview of developer journey to Production access</t>
+  </si>
+  <si>
+    <t>Product build</t>
+  </si>
+  <si>
+    <t>Testing requirements</t>
+  </si>
+  <si>
+    <t>Production Approvals Checklist</t>
+  </si>
+  <si>
+    <t>Sandbox testing</t>
+  </si>
+  <si>
+    <t>Multiple agents</t>
+  </si>
+  <si>
+    <t>Main and supporting agent access</t>
+  </si>
+  <si>
+    <t>Implementing agent types</t>
+  </si>
+  <si>
+    <t>Supporting customers in Making Tax Digital for Income Tax</t>
+  </si>
+  <si>
+    <t>API lifecycle and deprecation</t>
+  </si>
+  <si>
+    <t>API status</t>
+  </si>
+  <si>
+    <t>Breaking changes</t>
+  </si>
+  <si>
+    <t>Deprecating APIs</t>
+  </si>
+  <si>
+    <t>Indicating deprecation in headers</t>
+  </si>
+  <si>
+    <t>Retiring APIs</t>
+  </si>
+  <si>
+    <t>End-to-end customer journey</t>
+  </si>
+  <si>
+    <t>Customers and agents preparing for Making Tax Digital for Income Tax</t>
+  </si>
+  <si>
+    <t>Expand Customers and agents preparing for Making Tax Digital for Income Tax</t>
+  </si>
+  <si>
+    <t>Making updates during the tax year</t>
+  </si>
+  <si>
+    <t>Expand Making updates during the tax year</t>
+  </si>
+  <si>
+    <t>Tax calculations</t>
+  </si>
+  <si>
+    <t>Expand Tax calculations</t>
+  </si>
+  <si>
+    <t>Tasks outside MTD software</t>
+  </si>
+  <si>
+    <t>Expand Tasks outside MTD software</t>
+  </si>
+  <si>
+    <t>Making updates at the end of a tax year</t>
+  </si>
+  <si>
+    <t>Expand Making updates at the end of a tax year</t>
+  </si>
+  <si>
+    <t>Viewing a customer’s Self Assessment account information</t>
+  </si>
+  <si>
+    <t>Making Tax Digital for Income Tax terminology (style guide)</t>
+  </si>
+  <si>
+    <t>Expand Making Tax Digital for Income Tax terminology (style guide)</t>
+  </si>
+  <si>
+    <t>For the customer to complete the end-to-end journey, we expect Making Tax Digital for Income Tax-compatible software products to facilitate the entire journey for all income types, either in a single product covering the below requirements or through a number of products collectively meeting the below functionalities:</t>
+  </si>
+  <si>
+    <t>provide HMRC with transaction monitoring fraud prevention header data</t>
+  </si>
+  <si>
+    <t>obtain business ID unique to each of the customer’s businesses</t>
+  </si>
+  <si>
+    <t>create and maintain all digital records (or digitally link to a product that can do so) that a customer is required to keep by law in digital form - as per the terms of use, end users should own and have access to all their records created and be able to export these records, if necessary</t>
+  </si>
+  <si>
+    <t>submit quarterly update information for each mandated business income source (self-employment, multiple self-employments, UK property income and/or foreign property income)</t>
+  </si>
+  <si>
+    <t>allow customers to view an estimate of their income tax liability by either signposting them to their HMRC account or by displaying it in software - if the latter, the estimate must be presented with a disclaimer as to its accuracy</t>
+  </si>
+  <si>
+    <t>make required adjustments and finalise business income for the year</t>
+  </si>
+  <si>
+    <t>brought forward, carry forward or set sideways (when permitted) business losses occurring in any one year as well as to apply losses incurred in earlier years against current year profits</t>
+  </si>
+  <si>
+    <t>submit non-mandated income sources or divert customers to software where any unsupported non-mandated income sources can be included</t>
+  </si>
+  <si>
+    <t>make a final declaration or divert a customer to software where they can make it</t>
+  </si>
+  <si>
+    <t>The Making Tax Digital for Income Tax APIs that include the endpoints for the above functionality are:</t>
+  </si>
+  <si>
+    <t>Business Details</t>
+  </si>
+  <si>
+    <t>Business Source Adjustable Summary</t>
+  </si>
+  <si>
+    <t>Individual Calculations</t>
+  </si>
+  <si>
+    <t>Individual Losses</t>
+  </si>
+  <si>
+    <t>Obligations</t>
+  </si>
+  <si>
+    <t>Property Business</t>
+  </si>
+  <si>
+    <t>Self-Employment Business</t>
+  </si>
+  <si>
+    <t>HMRC will be providing tailored feedback messaging through nudges and prompts that software providers can incorporate into their software to support customers with their tax affairs. This is known as HMRC Assist. We encourage software providers to build meaningful prompts and nudges into their software products to support the customer journey and drive compliant behaviours.</t>
+  </si>
+  <si>
+    <t>In addition, software providers may wish to offer other functionality over and above the minimum standards. This could include automated functionality, for example, automated quarterly updates. Where this is the case, customers remain legally responsible for meeting their quarterly obligations, and HMRC would expect appropriate safeguards to be built in.</t>
+  </si>
+  <si>
+    <t>Your feedback matters! Share your thoughts and help us improve. Click here to complete a survey.</t>
+  </si>
+  <si>
+    <t>It is a legal requirement for software to provide compliant fraud prevention header information for all Making Tax Digital for Income Tax APIs. This requirement must be fulfilled before Production access to the APIs can be granted.</t>
+  </si>
+  <si>
+    <t>HMRC must see evidence that your software sends fraud prevention headers and must be satisfied with their level of accuracy. Before you start developing your Making Tax Digital for Income Tax-compatible software, we recommend you check whether your technology stack supports the collection of all header data required. For more guidance on fraud prevention headers, refer to Send fraud prevention data (GOV.UK).</t>
+  </si>
+  <si>
+    <t>If you are creating a new Production application, you must comply with our terms of use before we can issue you with Production credentials.</t>
+  </si>
+  <si>
+    <t>Sign into the Developer Hub and register your application for Sandbox testing.</t>
+  </si>
+  <si>
+    <t>Create a test user which is an individual to create test data.</t>
+  </si>
+  <si>
+    <t>Review the API documentation and this guide.</t>
+  </si>
+  <si>
+    <t>Develop your software application. Any queries during this phase should be sent to SDSTeam@hmrc.gov.uk.</t>
+  </si>
+  <si>
+    <t>Register your application for Production credentials by creating a Production application within your HMRC Developer Hub account. Alternatively, if you already have an existing Production application, you should add the relevant API subscriptions to it.</t>
+  </si>
+  <si>
+    <t>Test the software in the Sandbox and provide credentials used for testing to HMRC.</t>
+  </si>
+  <si>
+    <t>Complete and return the Production Approvals Checklist issued to you by HMRC.</t>
+  </si>
+  <si>
+    <t>HMRC will review the developer testing (including fraud header validity) and the completed Production Approvals Checklist:</t>
+  </si>
+  <si>
+    <t>if satisfactory, you will be granted Production access to the requested APIs</t>
+  </si>
+  <si>
+    <t>if not satisfactory, HMRC will contact you to advise what action is required</t>
+  </si>
+  <si>
+    <t>You can build the following 3 types of products:</t>
+  </si>
+  <si>
+    <t>full end-to-end product</t>
+  </si>
+  <si>
+    <t>in-year product</t>
+  </si>
+  <si>
+    <t>end-of-year product</t>
+  </si>
+  <si>
+    <t>Full end-to-end product</t>
+  </si>
+  <si>
+    <t>Software providers have the option to either build all elements required to meet minimum functionality standards in one go or to build these elements iteratively. If you choose to build iteratively, you are required to test the relevant APIs and complete the Production Approvals Checklist for each stage of the build.</t>
+  </si>
+  <si>
+    <t>For a full end-to-end product, there are 2 distinct stages and the following APIs are required for each one:</t>
+  </si>
+  <si>
+    <t>In-year functionality (submitting quarterly updates):</t>
+  </si>
+  <si>
+    <t>Business Details (MTD)</t>
+  </si>
+  <si>
+    <t>Obligations (MTD)</t>
+  </si>
+  <si>
+    <t>Self-Employment Business(MTD) and/or Property Business (MTD)</t>
+  </si>
+  <si>
+    <t>Individual Calculations (MTD) - if displaying calculation in software and not signposting customers to their HMRC account</t>
+  </si>
+  <si>
+    <t>End-of-year functionality:</t>
+  </si>
+  <si>
+    <t>Self-Employment Business(MTD) and/or Property Business (MTD) - if including annual submission endpoints in end-of-year build</t>
+  </si>
+  <si>
+    <t>Business Source Adjustable Summary (MTD)</t>
+  </si>
+  <si>
+    <t>Individual Losses (MTD)</t>
+  </si>
+  <si>
+    <t>Obligations (MTD) - if supporting final declaration</t>
+  </si>
+  <si>
+    <t>Individual Calculations (MTD) - if supporting final declaration in software and not diverting customers into a channel where they can submit it</t>
+  </si>
+  <si>
+    <t>In-year product</t>
+  </si>
+  <si>
+    <t>The following APIs are required:</t>
+  </si>
+  <si>
+    <t>End-of-year product</t>
+  </si>
+  <si>
+    <t>Self-Employment Business(MTD) and/or Property Business (MTD) - annual submission endpoints</t>
+  </si>
+  <si>
+    <t>Obligations (MTD) – if supporting final declaration</t>
+  </si>
+  <si>
+    <t>HMRC requires software providers to test all the API endpoints to which they need access. The following guidelines apply to accessing new API subscriptions and version updates of existing API subscriptions.</t>
+  </si>
+  <si>
+    <t>For APIs included in the minimum functionality standards:</t>
+  </si>
+  <si>
+    <t>you are required to test all endpoints shown within the documentation</t>
+  </si>
+  <si>
+    <t>ensure it aligns with the information in your completed Production Approvals Checklist</t>
+  </si>
+  <si>
+    <t>For APIs not included in the minimum functionality standards:</t>
+  </si>
+  <si>
+    <t>you are required to test only the endpoints relating to the data sources that your software supports</t>
+  </si>
+  <si>
+    <t>if your software does not support all data items, please notify SDSTeam@hmrc.gov.uk separately to confirm which data items you do support, so we can take this into account when checking the testing logs</t>
+  </si>
+  <si>
+    <t>Fraud prevention headers must be included in Sandbox calls, which will be checked by a specialist team. Once testing is complete, please send details of the dummy National Insurance Number used in the Sandbox to SDSTeam@hmrc.gov.uk. You will need to contact us within 14 days of completing your API testing to enable us to view the data within our logs.</t>
+  </si>
+  <si>
+    <t>HMRC will issue a Production Approvals Checklist asking for details about your software. This must be completed and returned to the software developer support team.</t>
+  </si>
+  <si>
+    <t>Production access will be granted after we are satisfied that:</t>
+  </si>
+  <si>
+    <t>the relevant APIs and endpoints have been tested satisfactorily</t>
+  </si>
+  <si>
+    <t>calls include compliant fraud prevention headers</t>
+  </si>
+  <si>
+    <t>the Checklist is completed satisfactorily and aligns with the testing</t>
+  </si>
+  <si>
+    <t>For access to updated APIs (that is, new versions), we do not generally require a new Production Approvals Checklist but do need to see evidence of satisfactory testing.</t>
+  </si>
+  <si>
+    <t>Note: It is important to build relevant error responses in your software to handle exceptions.</t>
+  </si>
+  <si>
+    <t>Some APIs in the Sandbox environment allow software to test different scenarios by including ‘Gov-Test-Scenario’ headers in requests. The Making Tax Digital for Income Tax API documentation provides more information about how to use these test scenarios.</t>
+  </si>
+  <si>
+    <t>Dynamic scenarios</t>
+  </si>
+  <si>
+    <t>Dynamic scenarios return a response that changes depending on the parameters submitted by software, for example National Insurance number or tax year. However, the submitted data is not stored for future requests and does not affect the behaviour of other endpoints.</t>
+  </si>
+  <si>
+    <t>Stateful scenarios</t>
+  </si>
+  <si>
+    <t>Stateful scenarios work across groups of endpoints.</t>
+  </si>
+  <si>
+    <t>With a stateful test scenario, you can submit custom data and then retrieve or list it from a different endpoint. For example, you can submit test data through the Self-Employment Business API, and then request a summary using the Business Source Adjustable Summary API for the same business.</t>
+  </si>
+  <si>
+    <t>The Sandbox environment retains test data you submit for 7 days after submission, after which it is deleted automatically.</t>
+  </si>
+  <si>
+    <t>Stateful Sandbox user journey</t>
+  </si>
+  <si>
+    <t>To test the journey for making a Self-Employment or Property Business submission and requesting a Business Source Adjustable Summary (BSAS), complete the following steps:</t>
+  </si>
+  <si>
+    <t>Submit 4 stateful Self-Employment/Property Business Period Summaries (one for each quarter of the same tax year) for the desired National Insurance number, tax year and Business ID by calling one of the following endpoints:</t>
+  </si>
+  <si>
+    <t>Create a Self-Employment Period Summary</t>
+  </si>
+  <si>
+    <t>Create a UK Property Income &amp; Expenses Period Summary</t>
+  </si>
+  <si>
+    <t>Create a Foreign Property Income &amp; Expenses Period Summary</t>
+  </si>
+  <si>
+    <t>Submit one stateful Self-Employment/Property Business Annual Submission for the same National Insurance number, tax year and Business ID by calling one of the following endpoints:</t>
+  </si>
+  <si>
+    <t>Create and Amend Self-Employment Annual Submission</t>
+  </si>
+  <si>
+    <t>Create and Amend a UK Property Business Annual Submission</t>
+  </si>
+  <si>
+    <t>Create and Amend a Foreign Property Annual Submission</t>
+  </si>
+  <si>
+    <t>Trigger a stateful Business Source Adjustable Summary for Self-Employment/Property business for the same National Insurance number and Business ID by calling the Trigger a Business Source Adjustable Summary endpoint.</t>
+  </si>
+  <si>
+    <t>Retrieve a stateful Business Source Adjustable Summary for the Self-Employment/Property Business by using the calculation ID generated in the previous step and calling one of the following endpoints:</t>
+  </si>
+  <si>
+    <t>Retrieve a Self-Employment Business Source Adjustable Summary (BSAS)</t>
+  </si>
+  <si>
+    <t>Retrieve a UK Property Business Source Adjustable Summary (BSAS)</t>
+  </si>
+  <si>
+    <t>Retrieve a Foreign Property Business Source Adjustable Summary (BSAS)</t>
+  </si>
+  <si>
+    <t>Submit a stateful accounting adjustment for Self-Employment/Property Business by using the same Business ID and calculation ID and calling one of the following endpoints:</t>
+  </si>
+  <si>
+    <t>Submit Self-Employment Accounting Adjustments</t>
+  </si>
+  <si>
+    <t>Submit UK Property Accounting Adjustments</t>
+  </si>
+  <si>
+    <t>Submit Foreign Property Accounting Adjustments</t>
+  </si>
+  <si>
+    <t>List all stateful Business Source Adjustable Summaries requested for the specific Business ID by calling the List Business Source Adjustable Summaries endpoint.</t>
+  </si>
+  <si>
+    <t>Stateful journey to request a Business Source Adjustable Summary</t>
+  </si>
+  <si>
+    <t>Open the stateful journey diagram in a new tab.</t>
+  </si>
+  <si>
+    <t>Previously, customers could have only one active agent registered to act on their behalf. With the implementation of multiple agent support, customers can now have several agents with different levels of access.</t>
+  </si>
+  <si>
+    <t>There are 2 types of agent:</t>
+  </si>
+  <si>
+    <t>Main agent: full access to all services, can do all tax-related filings including making final declarations, and can view tax calculations. Only one main agent is allowed at a time for a given customer.</t>
+  </si>
+  <si>
+    <t>Supporting agent: more limited access, can submit in-year updates but cannot make final declarations and Self Assessment filings or view calculations. Multiple supporting agents are allowed for each customer.</t>
+  </si>
+  <si>
+    <t>Customers are able to authorise a main agent and multiple supporting agents to act on their behalf. This provides more flexibility in managing their tax affairs.</t>
+  </si>
+  <si>
+    <t>An agent cannot be both main and supporting for the same customer.</t>
+  </si>
+  <si>
+    <t>An agent can be the main agent for one customer and a supporting agent for another.</t>
+  </si>
+  <si>
+    <t>Main agents have access to a larger set of APIs and endpoints than supporting agents. This ensures that sensitive information and critical actions are restricted to the main agent, while still allowing supporting agents to perform necessary tasks.</t>
+  </si>
+  <si>
+    <t>Main agents have access to all Making Tax Digital for Income Tax APIs.</t>
+  </si>
+  <si>
+    <t>Supporting agents have more restricted access.</t>
+  </si>
+  <si>
+    <t>The following APIs are available to supporting agents. For some APIs, supporting agents can only use some of the endpoints, as indicated.</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>Endpoints available to</t>
+  </si>
+  <si>
+    <t>supporting agent</t>
+  </si>
+  <si>
+    <t>CIS Deductions</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>Individuals Expenses</t>
+  </si>
+  <si>
+    <t>Individuals Losses</t>
+  </si>
+  <si>
+    <t>Other Deductions</t>
+  </si>
+  <si>
+    <t>Self Assessment BISS</t>
+  </si>
+  <si>
+    <t>Self Assessment BSAS</t>
+  </si>
+  <si>
+    <t>Self Assessment Individual Details</t>
+  </si>
+  <si>
+    <t>Self Employment Business</t>
+  </si>
+  <si>
+    <t>Individuals Reliefs</t>
+  </si>
+  <si>
+    <t>Create and Amend Relief Investments,</t>
+  </si>
+  <si>
+    <t>Retrieve Relief Investments,</t>
+  </si>
+  <si>
+    <t>Delete Relief Investments,</t>
+  </si>
+  <si>
+    <t>Create and Amend Other Reliefs,</t>
+  </si>
+  <si>
+    <t>Retrieve Other Reliefs,</t>
+  </si>
+  <si>
+    <t>Delete Other Reliefs,</t>
+  </si>
+  <si>
+    <t>Create and Amend Foreign Reliefs,</t>
+  </si>
+  <si>
+    <t>Retrieve Foreign Reliefs,</t>
+  </si>
+  <si>
+    <t>Delete Foreign Reliefs</t>
+  </si>
+  <si>
+    <t>Making Tax Digital for Income Tax APIs enforce agent type authorisation by determining the type of agent (main or supporting).</t>
+  </si>
+  <si>
+    <t>If a supporting agent tries to use an endpoint that is not allowed for supporting agents, the API will return a 403 CLIENT_OR_AGENT_NOT_AUTHORISED error.</t>
+  </si>
+  <si>
+    <t>Your software can check what type of agent is logged in with the Agent Authorisation API Get Status of a Relationship endpoint.</t>
+  </si>
+  <si>
+    <t>The customer support model guides HMRC customers to the most appropriate support. Check GOV.UK and the software provider’s guidance first.</t>
+  </si>
+  <si>
+    <t>Customers who have signed up to the Making Tax Digital for Income Tax testing phase will be given contact details for a dedicated Customer Support Team who are available from 8am to 6pm Monday to Friday.</t>
+  </si>
+  <si>
+    <t>We aim to respond to queries that are not resolved at the point of contact within 2 days, and to provide further updates, if required, every 2 working days.</t>
+  </si>
+  <si>
+    <t>Each Making Tax Digital for Income Tax API follows a lifecycle from the point where it is first published to the point where it is retired.</t>
+  </si>
+  <si>
+    <t>More specifically, every version of each API follows a lifecycle. Different versions of the same API can be at different points in the lifecycle. For example, v1.0 might be retired, v2.0 might be stable and v3.0 might be in beta.</t>
+  </si>
+  <si>
+    <t>The following table provides details about possible API statuses.</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Meaning</t>
+  </si>
+  <si>
+    <t>Documentation visible?</t>
+  </si>
+  <si>
+    <t>Can be subscribed to in Developer Hub?</t>
+  </si>
+  <si>
+    <t>Endpoints enabled?</t>
+  </si>
+  <si>
+    <t>Alpha</t>
+  </si>
+  <si>
+    <t>Early prototype - documentation only, available in External Test. Intended for feedback about the initial API design and documentation. Expect breaking changes and behaviour changes.</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Beta</t>
+  </si>
+  <si>
+    <t>Live service but not stable. Breaking changes and behaviour changes are possible.</t>
+  </si>
+  <si>
+    <t>Stable</t>
+  </si>
+  <si>
+    <t>Stable live service. No breaking changes and only minor behaviour changes.</t>
+  </si>
+  <si>
+    <t>Deprecated</t>
+  </si>
+  <si>
+    <t>Set to be retired, either because a new version of the API is available or because the API is no longer supported. If applicable, a new version of the API will be available in external test when the current version is deprecated.</t>
+  </si>
+  <si>
+    <t>Yes (see note)</t>
+  </si>
+  <si>
+    <t>Retired</t>
+  </si>
+  <si>
+    <t>API is no longer in use.</t>
+  </si>
+  <si>
+    <t>Note: If all versions of an API are deprecated, it no longer appears on the list of APIs unless you are signed in to the Developer Hub and have an active subscription to that API. You can still access the API documentation directly without being signed in.</t>
+  </si>
+  <si>
+    <t>Any change that might break software that relies on an API is counted as breaking change.</t>
+  </si>
+  <si>
+    <t>The following table lists the types of changes that we consider breaking.</t>
+  </si>
+  <si>
+    <t>Area</t>
+  </si>
+  <si>
+    <t>Query Parameter</t>
+  </si>
+  <si>
+    <t>Adding mandatory query parameter</t>
+  </si>
+  <si>
+    <t>Removing a query parameter</t>
+  </si>
+  <si>
+    <t>Renaming a query parameter</t>
+  </si>
+  <si>
+    <t>Changing an optional query parameter to be mandatory</t>
+  </si>
+  <si>
+    <t>Removing/renaming a value from an enum</t>
+  </si>
+  <si>
+    <t>Request Body</t>
+  </si>
+  <si>
+    <t>Adding a mandatory field</t>
+  </si>
+  <si>
+    <t>Removing a field</t>
+  </si>
+  <si>
+    <t>Renaming a field</t>
+  </si>
+  <si>
+    <t>Changing an optional field to be mandatory</t>
+  </si>
+  <si>
+    <t>Response Body</t>
+  </si>
+  <si>
+    <t>Changing a mandatory field to be optional</t>
+  </si>
+  <si>
+    <t>Adding/renaming a value to an enum</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Changing the URL of the endpoint</t>
+  </si>
+  <si>
+    <t>Removing a resource/endpoint</t>
+  </si>
+  <si>
+    <t>Changing the semantics of a field value (for example, the value returned changes from inclusive of VAT to exclusive of VAT)</t>
+  </si>
+  <si>
+    <t>Changing validation to have stronger constraints</t>
+  </si>
+  <si>
+    <t>Changes to errors</t>
+  </si>
+  <si>
+    <t>When we make changes to errors, we will not usually change the JSON structure returned. In the rare case when this is necessary, this will be considered a breaking change. The values of the error fields may change.</t>
+  </si>
+  <si>
+    <t>The following table outlines which types of changes to errors are treated as breaking changes and which are not.</t>
+  </si>
+  <si>
+    <t>Breaking changes for errors</t>
+  </si>
+  <si>
+    <t>Non-breaking changes for errors</t>
+  </si>
+  <si>
+    <t>Changing the HTTP status code to a different value</t>
+  </si>
+  <si>
+    <t>Removing an error code</t>
+  </si>
+  <si>
+    <t>Renaming an error code</t>
+  </si>
+  <si>
+    <t>Changing the message of an error</t>
+  </si>
+  <si>
+    <t>Adding a new error code (but see below)</t>
+  </si>
+  <si>
+    <t>If we add a new error code to an endpoint as part of a new field/object, which is not itself a breaking change, the new error is not counted as a breaking change.</t>
+  </si>
+  <si>
+    <t>For example, if we add a new optional string field to the request body and the field must satisfy a specific condition (otherwise, it fails with a new error); this error is not considered a breaking change because existing software will keep functioning as the error will only be returned if the new field is used.</t>
+  </si>
+  <si>
+    <t>If an API has been in production with a status of ‘Stable’, we aim for a deprecation period of 6 months.</t>
+  </si>
+  <si>
+    <t>For an API in beta, we aim for a deprecation period of a minimum of 6 weeks.</t>
+  </si>
+  <si>
+    <t>Applications cannot subscribe to a deprecated API version, but can still call the API version if the subscription was made before the status changed.</t>
+  </si>
+  <si>
+    <t>The status of APIs is indicated in the API documentation.</t>
+  </si>
+  <si>
+    <t>For releases after January 2024, when an endpoint becomes deprecated, it will return the following response headers.</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Example value</t>
+  </si>
+  <si>
+    <t>Deprecation</t>
+  </si>
+  <si>
+    <t>The deprecation date/time for this endpoint, in IMF-fixdate format.</t>
+  </si>
+  <si>
+    <t>Sun, 01 Jan 2023 23:59:59 GMT</t>
+  </si>
+  <si>
+    <t>Sunset</t>
+  </si>
+  <si>
+    <t>(optional) The earliest date/time this endpoint will become unavailable after deprecation, in IMF-fixdate format.</t>
+  </si>
+  <si>
+    <t>Sun, 02 Jul 2023 23:59:59 GMT</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>Documentation URL for the relevant API</t>
+  </si>
+  <si>
+    <t>https://developer.service.hmrc.gov.uk/api-documentation/docs/api/service/individual-calculations-api</t>
+  </si>
+  <si>
+    <t>The ‘Sunset’ header contains the earliest date/time that the endpoint could be retired after being deprecated. Do not rely on the availability of the endpoint after this.</t>
+  </si>
+  <si>
+    <t>The ‘Sunset’ header may not be returned in some rare cases, such as when the retirement date for an endpoint is uncertain.</t>
+  </si>
+  <si>
+    <t>Older deprecation headers</t>
+  </si>
+  <si>
+    <t>In previous releases, deprecation status could be indicated with a ‘Deprecation’ response header like this.</t>
+  </si>
+  <si>
+    <t>This endpoint is deprecated. See the API documentation.</t>
+  </si>
+  <si>
+    <t>Note: This was implemented only for the Business Source Adjustable Summary API.</t>
+  </si>
+  <si>
+    <t>After an API has been deprecated for the amounts of time indicated above, it can be retired and the endpoints and documentation will be removed. Ensure that your application does not rely on any deprecated APIs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> All content is available under the Open Government Licence v3.0, except where otherwise stated</t>
+  </si>
+  <si>
+    <t>© Crown copyright</t>
+  </si>
+  <si>
+    <t>© Crown copyright # # # hello. I am starting to build software for this. I am thinking to position myself as bridging software but i want to check with you if this idea fits with HMRC's requirements. A user would simply upload a csv or spreadsheet to my portal, AI would interpret all the transactions and then provide a draft preview of their quartely updates. The AI thing would be smart becasue it would understand if new duplicate data was being provided (i.e. an overlap with the last upload instance) and would act like a record-keeping portal but in actual fact, the user can really just continue using whatever method they've been doing before. If they really wanted to, they could just use my portal to add transactions but I intend to only capture the minimum required for MTD which is date, transaction type, amount, and a description (actually that last one is for the user's benefit only). 1. i don't know if that's acceptable product design can you tell me? 2. It says i can be an in-year or full-year etc etc what does that mean? 3. i'm just an accountant with little software programming knowledge, I'm just using ai to help me build everything. So far i already have a functioning website and I have the HMRC link working for HMRC test users. 4. I've set up a company already and will register with ico. is there something else I must do? 5. I notice other bridging software actually link to their excel sheets like a plugin, i want to not hassle the user with this sort of thing is that feasible or is this actually the only acceptable way according to MTD? I know you cannot copy paste etc thats the whole idea. 6. Anything else I need to know/am forgetting here? Do deep research. Don't lecture me on what MTD is though, im interested in the finer details that you've backup now. Before you answer, can you ask me at least 10 brief clarifying questions?</t>
+  </si>
+  <si>
+    <t>1. unrepresented taxpayers. 2. I don't know. I think just qtr updates but im not sure if thats allowed, perhaps i have to offer final decleratin do i? 3. i think bridging with lightweight record keeping yes 4. well i think i could offer all of that since ai could read everything but i would encourage primarily excel/google sheets/csvs for simplicity. 5. whatever the legal requirement is i think 6 or 7 years? 6. yes definitely i will say they must review and ensure its all correct 7. yes 8. all of those. 9. accountants can use yes 10. i think it will position itself as reading but it will offer adding transactions if user wants. 11. yes 12. ai will mostly be able to deal with duplicates, amendments to submitted quarters will be ok according to HMRC rules. 13. so, yes i think the ai could easily work out date, type, amount etc but i dont think its needs to do much more of a comprehensive business/private splits, adjustments, and tax treatment does it? 14. yes i have working versions. 15. well i dont know what it is can you tell me? 16. just start with feasibility.</t>
+  </si>
+  <si>
+    <t>Making Tax Digital for Income Tax service guide</t>
+  </si>
+  <si>
+    <t>API Endpoints available to</t>
+  </si>
+  <si>
+    <t>CIS Deductions All</t>
+  </si>
+  <si>
+    <t>Individuals Expenses All</t>
+  </si>
+  <si>
+    <t>Individuals Losses All</t>
+  </si>
+  <si>
+    <t>Obligations All</t>
+  </si>
+  <si>
+    <t>Other Deductions All</t>
+  </si>
+  <si>
+    <t>Self Assessment BISS All</t>
+  </si>
+  <si>
+    <t>Self Assessment BSAS All</t>
+  </si>
+  <si>
+    <t>Self Assessment Individual Details All</t>
+  </si>
+  <si>
+    <t>Self Employment Business All</t>
+  </si>
+  <si>
+    <t>Property Business All</t>
+  </si>
+  <si>
+    <t>Business Details All</t>
+  </si>
+  <si>
+    <t>Individuals Reliefs Create and Amend Relief Investments,</t>
+  </si>
+  <si>
+    <t>Status Meaning Documentation visible? Can be subscribed to in Developer Hub? Endpoints enabled?</t>
+  </si>
+  <si>
+    <t>Alpha Early prototype - documentation only, available in External Test. Intended for feedback about the initial API design and documentation. Expect breaking changes and behaviour changes. Yes No No</t>
+  </si>
+  <si>
+    <t>Beta Live service but not stable. Breaking changes and behaviour changes are possible. Yes Yes Yes</t>
+  </si>
+  <si>
+    <t>Stable Stable live service. No breaking changes and only minor behaviour changes. Yes Yes Yes</t>
+  </si>
+  <si>
+    <t>Deprecated Set to be retired, either because a new version of the API is available or because the API is no longer supported. If applicable, a new version of the API will be available in external test when the current version is deprecated. Yes (see note) No Yes</t>
+  </si>
+  <si>
+    <t>Retired API is no longer in use. No No No</t>
+  </si>
+  <si>
+    <t>Area Breaking changes</t>
+  </si>
+  <si>
+    <t>Breaking changes for errors Non-breaking changes for errors</t>
+  </si>
+  <si>
+    <t>Changing the HTTP status code to a different value Removing an error code</t>
+  </si>
+  <si>
+    <t>Renaming an error code Changing the message of an error</t>
+  </si>
+  <si>
+    <t>Name Meaning Example value</t>
+  </si>
+  <si>
+    <t>Deprecation The deprecation date/time for this endpoint, in IMF-fixdate format. Sun, 01 Jan 2023 23:59:59 GMT</t>
+  </si>
+  <si>
+    <t>Sunset (optional) The earliest date/time this endpoint will become unavailable after deprecation, in IMF-fixdate format. Sun, 02 Jul 2023 23:59:59 GMT</t>
+  </si>
+  <si>
+    <t>Link Documentation URL for the relevant API https://developer.service.hmrc.gov.uk/api-documentation/docs/api/service/individual-calculations-api</t>
+  </si>
+  <si>
+    <t>Name Example value</t>
+  </si>
+  <si>
+    <t>Deprecation This endpoint is deprecated. See the API documentation.</t>
+  </si>
+  <si>
+    <t>Yes — here are the questions I need so I can assess the design properly against HMRC’s rules and the practical approval path.</t>
+  </si>
+  <si>
+    <t>1. Are you planning this as software for unrepresented taxpayers, for your own accountancy clients, or for both?</t>
+  </si>
+  <si>
+    <t>2. Will your product support only quarterly submissions at first, or also end-of-year adjustments, losses, and final declaration?</t>
+  </si>
+  <si>
+    <t>3. Are you intending to be pure “bridging” software, or more of a lightweight bookkeeping/record-keeping layer with filing?</t>
+  </si>
+  <si>
+    <t>4. Will users upload only CSV/XLSX files, or also PDFs, bank exports, bookkeeping exports, emailed statements, or photos?</t>
+  </si>
+  <si>
+    <t>5. For each business, do you plan to store transaction-level records permanently, or only long enough to generate/update quarter totals?</t>
+  </si>
+  <si>
+    <t>6. Will the user be able to review, edit, approve, and override AI categorisation before anything is submitted?</t>
+  </si>
+  <si>
+    <t>7. Will your system keep an audit trail showing what was uploaded, what AI inferred, what was changed by the user, and what was filed?</t>
+  </si>
+  <si>
+    <t>8. Are you targeting sole traders only at first, or also UK property, foreign property, and multiple businesses per person?</t>
+  </si>
+  <si>
+    <t>9. Do you want agents/accountants to file on behalf of clients through your software, or only direct customer filing initially?</t>
+  </si>
+  <si>
+    <t>10. Will your portal create and maintain the digital records itself, or do you see it as reading external records and then filing from them?</t>
+  </si>
+  <si>
+    <t>11. Are you planning to let users export all records and submission data from your portal in a usable format?</t>
+  </si>
+  <si>
+    <t>12. Will users be able to correct prior uploads, delete duplicates, and deal with overlaps across quarters?</t>
+  </si>
+  <si>
+    <t>13. Are you planning to rely on AI for category mapping only, or also for deciding business/private splits, adjustments, and tax treatment?</t>
+  </si>
+  <si>
+    <t>14. Do you already have a privacy policy, terms, processor/subprocessor list, and data retention/deletion policy drafted?</t>
+  </si>
+  <si>
+    <t>15. Are you building this as a regulated accountancy service plus software, or as software sold independently to the public?</t>
+  </si>
+  <si>
+    <t>16. Do you want me to assess feasibility only, or also give you a practical launch checklist: legal, compliance, product scope, HMRC approval, and technical architecture?</t>
+  </si>
+  <si>
+    <t>Reply however you like — even brief answers are enough — and then I’ll do the deep research pass properly.</t>
+  </si>
+  <si>
+    <t>FEASIBILITY ASSESSMENT: AI-powered MTD for Income Tax Bridging Software</t>
+  </si>
+  <si>
+    <t>Your core concept — feasible, but with specific constraints you need to understand.</t>
+  </si>
+  <si>
+    <t>Your idea is an AI-powered portal where unrepresented taxpayers upload CSVs/spreadsheets, AI interprets the transactions, and the software submits quarterly updates to HMRC via the MTD APIs. You want it to feel lightweight: users keep doing what they've always done, upload their data, and your system handles the rest. Here's where that lands against HMRC's actual rules.</t>
+  </si>
+  <si>
+    <t>1. In-year only product: YES, this is explicitly allowed</t>
+  </si>
+  <si>
+    <t>HMRC's developer guide explicitly defines three product types you can build: a full end-to-end product, an in-year product, or an end-of-year product. Software providers have the option to either build all elements required to meet minimum functionality standards in one go or to build these elements iteratively. HMRC Developer Hub</t>
+  </si>
+  <si>
+    <t>For an in-year product, you need these APIs: Business Details, Obligations, Self-Employment Business and/or Property Business, and optionally Individual Calculations if you display the tax estimate in-software rather than pointing users to their HMRC account.</t>
+  </si>
+  <si>
+    <t>So you do NOT have to offer final declaration at launch. You can build in-year only and either add final declaration later or divert users elsewhere for it. The minimum functionality standards say software must "make a final declaration or divert a customer to software where they can make it." HMRC Developer Hub That "divert" option is your escape hatch — you can tell users to complete their final declaration via HMRC online services or another product.</t>
+  </si>
+  <si>
+    <t>However, you need to be clear about this in your product and approval checklist. If you're in-year only, your users will still need to complete a final declaration somewhere by 31 January following the tax year end. The final declaration must be made by 31 January following the end of the tax year. GoSimpleTax Make sure your software clearly communicates this obligation so users don't think they're done after Q4.</t>
+  </si>
+  <si>
+    <t>2. CSV/spreadsheet upload as a "digital link": YES, this works</t>
+  </si>
+  <si>
+    <t>This is the critical design question and the answer is good news for you. HMRC listed CSV or XML import and export, including the downloading and uploading of files, as acceptable digital links. Sage Emailing a spreadsheet for import, using a memory stick, and CSV/XML transfers are all explicitly permitted.</t>
+  </si>
+  <si>
+    <t>What is NOT permitted is copy-and-paste or manual re-entry. Typing data manually doesn't count as a digital link under Making Tax Digital rules, including copy and pasting. Sage</t>
+  </si>
+  <si>
+    <t>So your model — user uploads a CSV/XLSX to your portal, AI reads it, software submits to HMRC — counts as a valid digital link chain. The key is that the data flows digitally from the user's spreadsheet through your system to HMRC without anyone retyping anything. Your AI reading and categorising the uploaded file is fine; it's still a digital transfer.</t>
+  </si>
+  <si>
+    <t>One nuance: if you enter key accounting data into a spreadsheet, then the digital link starts there. After this, the data must be transferred digitally. Xero So the user's spreadsheet IS the origin of the digital record. Your portal receives it digitally (upload), processes it digitally (AI), and submits it digitally (API). That chain is compliant.</t>
+  </si>
+  <si>
+    <t>You do NOT need to build an Excel plugin like some competitors. That's one approach but not the only acceptable one. File upload is equally valid.</t>
+  </si>
+  <si>
+    <t>3. What quarterly updates actually need to contain</t>
+  </si>
+  <si>
+    <t>This is simpler than you might think. For MTD for Income Tax the minimum information to be recorded is the date, amount and category of each business transaction. It is not required to submit full transactional data to HMRC, only a summary of the quarterly totals. TaxCalc</t>
+  </si>
+  <si>
+    <t>Even better for your target users: where under the VAT threshold, self-employed and landlords are only required to submit two figures, total income and total expenditure. Ross Martin So for businesses with annual turnover below £90,000, the quarterly update is literally just income total and expenses total. That's two numbers per business per quarter.</t>
+  </si>
+  <si>
+    <t>For those above the VAT threshold, you need category-level totals matching the SA103F (self-employment) or SA105 (property) categories. These are broadly: turnover/income, cost of goods, various expense categories (travel, office costs, advertising, etc.).</t>
+  </si>
+  <si>
+    <t>Crucially: there is no obligation to make tax or accounting adjustments as would be required in a full tax return. Quarterly updates do not require a taxpayer declaration, and penalties for inaccuracies do not apply. Dixonwilson This means the quarterly updates are genuinely just raw transaction summaries. No capital allowances, no business/private use splits, no tax adjustments. Those all happen at year-end in the final declaration.</t>
+  </si>
+  <si>
+    <t>This directly answers your question 13: for quarterly updates, your AI only needs to work out date, type, amount, and categorise against the SA103/SA105 categories. It does NOT need to handle business/private splits, capital allowances, or tax treatment at the quarterly stage. That's all final declaration territory.</t>
+  </si>
+  <si>
+    <t>4. Record keeping requirements</t>
+  </si>
+  <si>
+    <t>Your portal needs to store (or digitally link to) records containing: date, amount, and category of each income and expense item. Dixonwilson Individual transaction-level records, not just summaries.</t>
+  </si>
+  <si>
+    <t>HMRC would like to encourage records to be kept in as near to real time as possible. However, it will still be possible to create the digital records at quarterly intervals. ICAEW So your model of users uploading periodically is fine — they don't need to log transactions in real time.</t>
+  </si>
+  <si>
+    <t>For retention: you must keep your financial records for at least five years after the 31 January Self Assessment tax return submission deadline of the relevant tax year. GoSimpleTax So it's 5 years for self-employed/partnerships after the filing deadline, not 6 or 7. For the 2026/27 tax year (filed by 31 Jan 2028), records must be kept until at least 31 Jan 2033.</t>
+  </si>
+  <si>
+    <t>As the terms of use require: users must own and have access to all their records, and be able to export them. You confirmed you'll offer export — make sure this is robust.</t>
+  </si>
+  <si>
+    <t>5. The "in-year product" path and what you skip</t>
+  </si>
+  <si>
+    <t>By building in-year only, you avoid needing to implement:</t>
+  </si>
+  <si>
+    <t>Business Source Adjustable Summary (BSAS) — year-end accounting adjustments</t>
+  </si>
+  <si>
+    <t>Individual Losses — brought forward/carried forward/sideways losses</t>
+  </si>
+  <si>
+    <t>Individual Calculations final declaration trigger</t>
+  </si>
+  <si>
+    <t>Non-mandated income sources (dividends, savings, employment, etc.)</t>
+  </si>
+  <si>
+    <t>You would need to signpost users clearly: after Q4, they need to go to HMRC online services (or another product) to make adjustments, report other income, and submit their final declaration.</t>
+  </si>
+  <si>
+    <t>6. The automated submission point — HMRC explicitly allows it, with a caveat</t>
+  </si>
+  <si>
+    <t>Software providers may wish to offer other functionality over and above the minimum standards, including automated functionality, for example, automated quarterly updates. Where this is the case, customers remain legally responsible for meeting their quarterly obligations, and HMRC would expect appropriate safeguards to be built in. HMRC Developer Hub</t>
+  </si>
+  <si>
+    <t>You said users must review and approve before submission. This is exactly the right approach. Build a clear preview/approval step. Don't auto-submit without user confirmation — HMRC expects safeguards.</t>
+  </si>
+  <si>
+    <t>7. Fraud prevention headers — non-negotiable, legally required</t>
+  </si>
+  <si>
+    <t>You are required by law to submit header data for the Income Tax Self Assessment MTD APIs. If after discussions with HMRC an application continues to submit incorrect or missing data, software providers may be fined and blocked from using HMRC APIs. HMRC Developer Hub</t>
+  </si>
+  <si>
+    <t>This is a technical requirement you need to nail before Production access. The headers include client IP, timezone, browser details, device info, etc. Since your product is a web portal, you'll be using the WEB_APP_VIA_SERVER connection method. Make sure your tech stack can collect all required header data. HMRC will check this during your Production approval.</t>
+  </si>
+  <si>
+    <t>8. Production approval process</t>
+  </si>
+  <si>
+    <t>The path is: register on Developer Hub ? build in Sandbox ? test all endpoints ? submit fraud prevention headers for review ? complete Production Approvals Checklist ? HMRC reviews and grants access. HMRC will review the developer testing including fraud header validity and the completed Production Approvals Checklist. HMRC Developer Hub</t>
+  </si>
+  <si>
+    <t>You mentioned you already have the HMRC link working for test users — that's great, you're ahead of many. The Sandbox retains test data for 7 days.</t>
+  </si>
+  <si>
+    <t>9. Agent support</t>
+  </si>
+  <si>
+    <t>You want accountants to be able to use this for clients. HMRC supports both main and supporting agents. Main agents have full access to all services. Supporting agents have more limited access but can submit in-year updates. HMRC Developer Hub A supporting agent can submit quarterly updates, which aligns perfectly with your in-year product. You'll need to implement the OAuth agent authorisation flow.</t>
+  </si>
+  <si>
+    <t>10. Question 15 — "regulated accountancy service vs independent software"</t>
+  </si>
+  <si>
+    <t>Here's what I was getting at. There are two different business models:</t>
+  </si>
+  <si>
+    <t>Software sold independently: you build and sell MTD software to the public. You're a software provider. You don't need to be a regulated accountant or hold any professional body membership to do this. HMRC doesn't regulate who can build MTD software — they just approve it technically. You need ICO registration (which you have), GDPR compliance, and HMRC's Production approval.</t>
+  </si>
+  <si>
+    <t>Regulated accountancy service: if you're also providing tax advice, preparing returns, or acting as a tax agent, that's a different matter. Tax agents don't technically need to be regulated in the UK (unlike, say, audit), but HMRC has an agent services regime and professional bodies (ICAEW, ACCA, ATT, CIOT) have conduct requirements for their members.</t>
+  </si>
+  <si>
+    <t>Since you said you're an accountant, the question is whether your software product crosses into providing tax advice or preparation services. If your AI is just categorising transactions and generating draft summaries for the user to review, that's software. If you're (via the AI) telling users how to treat items for tax purposes, suggesting deductions, or making business/private split decisions, you're getting closer to advisory territory.</t>
+  </si>
+  <si>
+    <t>For a pure bridging/filing tool: you're fine as a software provider. No special regulation beyond HMRC approval, ICO, and standard business obligations. But be careful with your marketing — don't position the AI as giving tax advice.</t>
+  </si>
+  <si>
+    <t>11. Cumulative updates and duplicate handling</t>
+  </si>
+  <si>
+    <t>Good news on your duplicate handling idea. Quarterly updates are cumulative — your latest figures replace the previous ones. Mtd So each quarterly submission represents the year-to-date total, not just that quarter. If a user uploads overlapping data, your AI just needs to deduplicate and produce the correct cumulative total. If a mistake is found later, the next quarterly update simply overwrites the previous one with corrected cumulative figures.</t>
+  </si>
+  <si>
+    <t>Each update includes your totals for the year so far, so you can correct earlier quarters in later submissions. Xero You can also make as many submissions per quarter as you like — HMRC just takes the latest one.</t>
+  </si>
+  <si>
+    <t>12. Soft landing in year one</t>
+  </si>
+  <si>
+    <t>Helpful context: HMRC has confirmed a soft landing for the first year: penalty points will not be issued for late quarterly updates during 2026/27. ByteStart This gives you and your users breathing room in the first year. Late final declarations and inaccuracies still carry penalties from day one though.</t>
+  </si>
+  <si>
+    <t>KEY RISKS AND GAPS</t>
+  </si>
+  <si>
+    <t>Risk 1: Record-keeping responsibility. Your software must either "create and maintain all digital records" or "digitally link to a product that can do so." If you position as bridging, the user's spreadsheet is the record-keeping system and your portal bridges to HMRC. That's fine. But if users start adding transactions directly in your portal, your portal becomes a record-keeping system and you take on the obligation to store, preserve, and allow export of those records for 5+ years. Be intentional about which role you're playing.</t>
+  </si>
+  <si>
+    <t>Risk 2: AI categorisation accuracy. If AI miscategorises transactions, the user is still legally responsible — but if your software consistently produces wrong categories and users don't catch them, you'll face reputational and possibly legal exposure. Your review/approval step is essential, but consider also logging every AI categorisation decision for audit purposes.</t>
+  </si>
+  <si>
+    <t>Risk 3: Multiple income sources complexity. You said you want to support sole traders, UK property, foreign property, and multiple businesses. Each business requires separate quarterly updates. A user with a sole trade and two rental properties could need 12 quarterly updates a year (4 × 3 businesses). Make sure your AI can separate transactions by business source from a single uploaded file.</t>
+  </si>
+  <si>
+    <t>Risk 4: You still need to handle the "signpost to final declaration" piece properly. Don't just say "go to HMRC" — give users clear, actionable guidance on what they need to do and by when.</t>
+  </si>
+  <si>
+    <t>BOTTOM LINE</t>
+  </si>
+  <si>
+    <t>Your concept is feasible and HMRC-compliant. An in-year bridging product that accepts CSV/XLSX uploads, uses AI to categorise and summarise, shows users a preview, and submits quarterly updates via the MTD APIs is a legitimate product design. You can launch without final declaration support by diverting users to HMRC online services for year-end.</t>
+  </si>
+  <si>
+    <t>The digital link chain (spreadsheet ? file upload ? your AI ? HMRC API) satisfies HMRC's requirements. CSV upload is explicitly listed as an acceptable digital link. You don't need a plugin.</t>
+  </si>
+  <si>
+    <t>Your priority actions are: nail the fraud prevention headers, complete Sandbox testing of all required endpoints, prepare for the Production Approvals Checklist, and make sure your data retention and export capabilities are solid. The AI categorisation is the value-add but the compliance infrastructure is what gets you through the door.</t>
   </si>
 </sst>
 </file>
@@ -95,11 +2213,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -483,4 +2603,6621 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD021F67-FCE6-458E-BA86-4D2E0AB02015}">
+  <dimension ref="B2:B24"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9549A4D8-90E6-4474-AEE3-371AD3D49831}">
+  <dimension ref="B4:B511"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B8" s="2">
+        <v>1.9444444444444445E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B27" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B29" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B30" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B35" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B37" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B40" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B42" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B44" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B45" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B46" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B47" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B48" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B49" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B50" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B51" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B52" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B53" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B54" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B55" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B56" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B57" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B58" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B59" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B60" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B61" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B62" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B63" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B64" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B65" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B66" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B67" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B68" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B69" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B70" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B71" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B72" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B73" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B74" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B75" s="2">
+        <v>2.361111111111111E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B77" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B78" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B79" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B81" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B83" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B85" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B87" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B89" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B91" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B93" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="95" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B95" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B97" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B98" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B99" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B100" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B101" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B103" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B104" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B106" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B107" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B109" s="2">
+        <v>2.7083333333333334E-2</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B111" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B112" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B113" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B115" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B117" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B119" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B121" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B123" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B125" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B127" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B129" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B131" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B133" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B135" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B136" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B137" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B138" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B139" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B140" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B141" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B142" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B143" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B146" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B148" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B151" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B153" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B156" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B158" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B161" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B163" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B166" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B168" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B170" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B171" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B172" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B173" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B174" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B175" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B176" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B177" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B178" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B179" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B180" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B181" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B182" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B183" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B184" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B185" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B186" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="187" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B187" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B188" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="189" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B189" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B190" s="3">
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B191" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="192" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B192" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B193" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B194" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B195" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B196" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B197" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="198" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B198" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="199" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B199" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="200" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B200" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="201" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B201" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="202" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B202" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="203" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B203" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="204" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B204" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="205" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B205" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="206" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B206" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="207" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B207" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="208" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B208" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="209" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B209" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="210" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B210" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="211" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B211" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="212" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B212" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="213" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B213" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="214" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B214" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="215" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B215" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="216" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B216" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="217" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B217" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="218" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B218" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="219" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B219" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="220" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B220" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="221" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B221" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="222" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B222" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="223" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B223" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="224" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B224" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="225" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B225" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="226" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B226" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="227" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B227" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="228" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B228" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="229" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B229" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="230" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B230" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="231" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B231" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="232" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B232" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="233" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B233" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="234" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B234" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="235" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B235" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="236" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B236" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="237" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B237" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="238" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B238" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="239" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B239" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="240" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B240" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="241" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B241" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="242" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B242" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="243" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B243" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="244" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B244" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="245" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B245" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="246" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B246" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="247" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B247" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="248" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B248" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="249" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B249" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="250" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B250" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="251" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B251" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="252" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B252" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="253" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B253" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="254" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B254" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="255" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B255" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="256" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B256" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="257" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B257" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="258" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B258" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="259" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B259" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="260" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B260" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="261" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B261" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="262" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B262" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="263" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B263" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="264" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B264" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="265" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B265" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="266" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B266" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="267" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B267" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="268" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B268" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="269" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B269" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="271" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B271" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="272" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B272" s="2">
+        <v>3.1944444444444442E-2</v>
+      </c>
+    </row>
+    <row r="274" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B274" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="275" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B275" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="276" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B276" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="278" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B278" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="280" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B280" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="282" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B282" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="284" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B284" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="286" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B286" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="288" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B288" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="290" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B290" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="292" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B292" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="294" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B294" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="296" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B296" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="298" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B298" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="300" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B300" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="302" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B302" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="304" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B304" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="306" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B306" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="308" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B308" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="310" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B310" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="311" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B311" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="312" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B312" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="313" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B313" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="314" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B314" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="315" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B315" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="317" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B317" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="318" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B318" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="320" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B320" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="321" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B321" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="323" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B323" s="2">
+        <v>3.888888888888889E-2</v>
+      </c>
+    </row>
+    <row r="325" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B325" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="326" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B326" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="327" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B327" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="329" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B329" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="331" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B331" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="333" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B333" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="335" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B335" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="337" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B337" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="339" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B339" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="341" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B341" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="343" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B343" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="345" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B345" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="348" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B348" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="349" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B349" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="350" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B350" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="352" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B352" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="354" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B354" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="355" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B355" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="356" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B356" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="357" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B357" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="359" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B359" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="361" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B361" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="362" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B362" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="364" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B364" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="366" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B366" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="368" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B368" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="369" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B369" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="370" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B370" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="371" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B371" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="372" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B372" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="374" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B374" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="375" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B375" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="376" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B376" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="377" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B377" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="379" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B379" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="381" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B381" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="383" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B383" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="384" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B384" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="385" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B385" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="387" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B387" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="389" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B389" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="390" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B390" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="391" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B391" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="393" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B393" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="394" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B394" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="396" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B396" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="398" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B398" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="400" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B400" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="402" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B402" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="404" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B404" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="406" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B406" s="2">
+        <v>4.3055555555555555E-2</v>
+      </c>
+    </row>
+    <row r="408" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B408" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="409" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B409" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="410" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B410" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="412" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B412" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="414" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B414" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="417" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B417" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="418" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B418" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="419" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B419" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="421" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B421" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="423" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B423" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="424" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B424" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="425" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B425" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="426" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B426" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="428" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B428" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="430" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B430" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="431" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B431" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="433" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B433" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="435" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B435" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="437" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B437" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="438" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B438" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="440" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B440" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="441" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B441" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="443" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B443" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="444" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B444" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="445" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B445" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="447" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B447" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="449" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B449" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="451" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B451" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="453" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B453" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="455" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B455" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="456" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B456" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="457" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B457" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="459" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B459" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="460" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B460" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="461" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B461" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="463" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B463" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="464" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B464" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="465" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B465" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="467" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B467" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="469" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B469" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="471" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B471" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="473" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B473" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="475" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B475" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="477" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B477" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="478" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B478" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="479" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B479" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="481" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B481" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="483" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B483" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="485" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B485" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="487" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B487" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="489" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B489" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="490" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B490" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="491" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B491" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="492" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B492" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="493" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B493" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="494" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B494" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="495" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B495" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="496" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B496" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="498" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B498" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="500" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B500" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="501" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B501" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="502" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B502" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="503" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B503" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="507" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B507" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="511" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B511" t="s">
+        <v>336</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72F9FD5D-EAB0-4D90-9B4C-19DDCA4502BC}">
+  <dimension ref="B2:F347"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B20" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B21" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B22" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B23" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B24" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B25" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B26" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B27" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B29" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B31" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B33" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B34" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B35" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B37" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B39" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B40" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B42" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B43" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B44" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B45" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B46" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B47" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B48" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B49" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B50" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B51" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B52" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B53" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B54" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B56" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B57" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B58" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B59" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B60" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B62" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B64" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B66" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B67" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B68" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B69" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B70" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B72" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B73" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B74" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B75" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B76" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B77" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B78" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B80" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B81" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B82" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B83" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B84" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B85" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B87" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B88" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B89" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B90" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B91" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B92" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B93" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B94" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B96" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B98" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B99" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B100" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B102" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B103" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B104" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B106" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B107" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B109" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B111" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B112" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B113" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B114" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B116" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B118" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B120" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B121" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B123" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B124" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B126" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B127" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B129" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B131" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B133" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B134" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B136" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B138" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B139" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B140" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B141" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B143" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B144" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B145" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B146" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B148" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B150" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B151" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B152" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B153" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B155" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B156" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B157" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B158" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B160" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B162" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B164" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B166" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B167" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B169" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B171" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B172" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B173" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B175" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B177" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B179" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B181" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B182" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B184" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B186" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B188" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="189" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B189" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B190" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B191" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="192" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B192" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B193" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B194" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B195" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B196" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B197" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="198" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B198" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="199" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B199" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="200" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B200" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="201" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B201" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="202" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B202" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="203" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B203" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="204" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B204" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="205" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B205" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="206" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B206" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="207" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B207" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="208" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B208" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="209" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B209" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="210" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B210" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="211" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B211" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="213" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B213" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="215" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B215" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="217" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B217" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="218" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B218" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="220" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B220" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="222" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B222" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="224" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B224" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="225" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B225" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="227" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B227" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="229" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B229" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="230" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B230" t="s">
+        <v>520</v>
+      </c>
+      <c r="C230" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="232" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B232" t="s">
+        <v>521</v>
+      </c>
+      <c r="C232" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="233" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B233" t="s">
+        <v>526</v>
+      </c>
+      <c r="C233" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="234" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B234" t="s">
+        <v>530</v>
+      </c>
+      <c r="C234" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="235" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B235" t="s">
+        <v>532</v>
+      </c>
+      <c r="C235" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="236" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B236" t="s">
+        <v>534</v>
+      </c>
+      <c r="C236" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="237" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B237" t="s">
+        <v>537</v>
+      </c>
+      <c r="C237" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="238" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B238" t="s">
+        <v>539</v>
+      </c>
+      <c r="C238" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="239" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="C239" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="240" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B240" t="s">
+        <v>360</v>
+      </c>
+      <c r="C240" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="241" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B241" t="s">
+        <v>540</v>
+      </c>
+      <c r="C241" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="242" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="C242" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="243" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B243" t="s">
+        <v>541</v>
+      </c>
+      <c r="C243" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="245" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B245" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="246" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B246" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="247" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B247" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="248" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B248" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="249" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B249" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="250" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B250" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="251" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B251" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="252" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B252" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="253" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B253" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="254" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B254" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="255" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B255" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="256" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B256" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="257" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B257" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="258" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B258" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="259" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B259" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="260" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B260" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="261" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B261" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="262" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B262" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="263" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B263" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="264" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B264" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="265" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B265" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="266" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B266" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="267" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B267" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="268" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B268" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="269" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B269" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="271" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B271" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="273" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B273" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="274" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B274" t="s">
+        <v>567</v>
+      </c>
+      <c r="C274" t="s">
+        <v>522</v>
+      </c>
+      <c r="D274" t="s">
+        <v>523</v>
+      </c>
+      <c r="E274" t="s">
+        <v>524</v>
+      </c>
+      <c r="F274" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="275" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B275" t="s">
+        <v>569</v>
+      </c>
+      <c r="C275" t="s">
+        <v>527</v>
+      </c>
+      <c r="D275" t="s">
+        <v>528</v>
+      </c>
+      <c r="E275" t="s">
+        <v>529</v>
+      </c>
+      <c r="F275" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="276" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B276" t="s">
+        <v>571</v>
+      </c>
+      <c r="C276" t="s">
+        <v>531</v>
+      </c>
+      <c r="D276" t="s">
+        <v>528</v>
+      </c>
+      <c r="E276" t="s">
+        <v>528</v>
+      </c>
+      <c r="F276" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="277" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B277" t="s">
+        <v>572</v>
+      </c>
+      <c r="C277" t="s">
+        <v>533</v>
+      </c>
+      <c r="D277" t="s">
+        <v>528</v>
+      </c>
+      <c r="E277" t="s">
+        <v>528</v>
+      </c>
+      <c r="F277" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="278" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="C278" t="s">
+        <v>535</v>
+      </c>
+      <c r="D278" t="s">
+        <v>536</v>
+      </c>
+      <c r="E278" t="s">
+        <v>529</v>
+      </c>
+      <c r="F278" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="279" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B279" t="s">
+        <v>573</v>
+      </c>
+      <c r="C279" t="s">
+        <v>538</v>
+      </c>
+      <c r="D279" t="s">
+        <v>529</v>
+      </c>
+      <c r="E279" t="s">
+        <v>529</v>
+      </c>
+      <c r="F279" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="281" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B281" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="282" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B282" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="284" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B284" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="286" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B286" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="287" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="C287" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="288" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B288" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="290" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B290" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="291" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B291" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="293" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B293" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="294" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B294" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="295" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B295" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="296" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B296" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="297" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B297" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="299" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B299" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="301" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B301" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="302" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B302" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="304" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B304" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="305" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B305" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="306" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B306" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="308" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B308" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="309" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B309" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="311" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B311" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="313" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B313" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="314" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B314" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="315" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="C315" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="316" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="C316" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="317" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="C317" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="335" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C335" t="s">
+        <v>522</v>
+      </c>
+      <c r="D335" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="336" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C336" t="s">
+        <v>582</v>
+      </c>
+      <c r="D336" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="337" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C337" t="s">
+        <v>585</v>
+      </c>
+      <c r="D337" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="338" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C338" t="s">
+        <v>588</v>
+      </c>
+      <c r="D338" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="346" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C346" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="347" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C347" t="s">
+        <v>594</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96D94545-5399-43ED-8FD5-95242523BFEB}">
+  <dimension ref="B2:F354"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B20" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B21" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B22" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B23" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B24" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B25" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B26" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B27" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B28" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B29" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B30" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B31" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B32" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B33" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B34" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B35" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B36" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B37" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B38" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B39" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B40" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B41" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B42" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B43" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B44" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B45" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B46" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B48" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B49" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B50" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B51" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B52" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B53" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B54" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B55" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B56" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B57" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B59" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B60" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B61" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B62" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B63" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B64" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B65" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B66" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B67" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B69" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B71" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B73" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B74" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B75" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B77" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B79" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B80" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B82" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B83" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B84" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B85" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B86" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B87" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B88" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B89" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B90" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B91" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B92" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B93" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B94" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B96" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B97" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B98" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B99" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B100" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B102" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B104" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B106" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B107" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B108" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B109" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B110" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B112" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B113" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B114" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B115" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B116" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B117" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B118" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B120" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B121" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B122" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B123" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B124" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B125" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B127" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B128" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B129" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B130" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B131" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B132" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B133" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B134" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B136" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B138" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B139" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B140" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B142" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B143" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B144" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B146" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B147" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B149" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B151" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B152" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B153" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B154" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B156" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B158" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B160" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B161" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B163" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B164" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B166" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B167" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B169" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B171" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B173" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B174" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B176" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B178" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B179" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B180" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B181" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B183" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B184" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B185" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B186" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B188" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B190" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B191" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="192" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B192" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B193" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B195" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B196" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B197" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="198" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B198" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="200" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B200" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="202" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B202" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="204" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B204" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="206" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B206" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="207" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B207" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="209" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B209" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="211" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B211" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="212" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B212" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="213" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B213" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="215" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B215" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="217" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B217" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="219" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B219" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="221" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B221" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="222" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B222" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="224" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B224" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="226" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B226" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="228" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B228" t="s">
+        <v>490</v>
+      </c>
+      <c r="C228" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="229" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B229" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="230" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B230" t="s">
+        <v>493</v>
+      </c>
+      <c r="C230" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="231" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B231" t="s">
+        <v>495</v>
+      </c>
+      <c r="C231" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="232" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B232" t="s">
+        <v>496</v>
+      </c>
+      <c r="C232" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="233" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B233" t="s">
+        <v>393</v>
+      </c>
+      <c r="C233" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="234" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B234" t="s">
+        <v>497</v>
+      </c>
+      <c r="C234" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="235" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B235" t="s">
+        <v>498</v>
+      </c>
+      <c r="C235" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="236" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B236" t="s">
+        <v>499</v>
+      </c>
+      <c r="C236" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="237" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B237" t="s">
+        <v>500</v>
+      </c>
+      <c r="C237" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="238" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B238" t="s">
+        <v>501</v>
+      </c>
+      <c r="C238" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="239" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B239" t="s">
+        <v>394</v>
+      </c>
+      <c r="C239" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="240" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B240" t="s">
+        <v>389</v>
+      </c>
+      <c r="C240" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="241" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B241" t="s">
+        <v>502</v>
+      </c>
+      <c r="C241" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="242" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B242" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="243" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B243" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="244" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B244" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="245" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B245" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="246" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B246" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="247" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B247" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="248" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B248" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="249" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B249" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="250" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B250" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="251" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B251" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="253" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B253" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="255" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B255" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="257" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B257" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="258" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B258" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="260" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B260" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="262" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B262" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="264" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B264" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="265" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B265" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="267" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B267" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="269" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B269" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="270" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B270" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="272" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B272" t="s">
+        <v>521</v>
+      </c>
+      <c r="C272" t="s">
+        <v>522</v>
+      </c>
+      <c r="D272" t="s">
+        <v>523</v>
+      </c>
+      <c r="E272" t="s">
+        <v>524</v>
+      </c>
+      <c r="F272" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="273" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B273" t="s">
+        <v>526</v>
+      </c>
+      <c r="C273" t="s">
+        <v>527</v>
+      </c>
+      <c r="D273" t="s">
+        <v>528</v>
+      </c>
+      <c r="E273" t="s">
+        <v>529</v>
+      </c>
+      <c r="F273" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="274" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B274" t="s">
+        <v>530</v>
+      </c>
+      <c r="C274" t="s">
+        <v>531</v>
+      </c>
+      <c r="D274" t="s">
+        <v>528</v>
+      </c>
+      <c r="E274" t="s">
+        <v>528</v>
+      </c>
+      <c r="F274" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="275" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B275" t="s">
+        <v>532</v>
+      </c>
+      <c r="C275" t="s">
+        <v>533</v>
+      </c>
+      <c r="D275" t="s">
+        <v>528</v>
+      </c>
+      <c r="E275" t="s">
+        <v>528</v>
+      </c>
+      <c r="F275" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="276" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B276" t="s">
+        <v>534</v>
+      </c>
+      <c r="C276" t="s">
+        <v>535</v>
+      </c>
+      <c r="D276" t="s">
+        <v>536</v>
+      </c>
+      <c r="E276" t="s">
+        <v>529</v>
+      </c>
+      <c r="F276" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="277" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B277" t="s">
+        <v>537</v>
+      </c>
+      <c r="C277" t="s">
+        <v>538</v>
+      </c>
+      <c r="D277" t="s">
+        <v>529</v>
+      </c>
+      <c r="E277" t="s">
+        <v>529</v>
+      </c>
+      <c r="F277" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="278" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B278" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="280" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B280" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="281" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B281" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="283" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B283" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="285" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B285" t="s">
+        <v>542</v>
+      </c>
+      <c r="C285" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="286" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B286" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="287" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B287" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="288" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B288" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="289" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B289" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="290" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B290" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="291" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B291" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="292" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B292" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="293" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B293" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="294" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B294" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="295" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B295" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="296" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B296" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="297" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B297" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="298" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B298" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="299" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B299" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="300" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B300" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="301" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B301" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="302" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B302" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="303" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B303" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="304" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B304" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="305" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B305" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="306" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B306" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="307" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B307" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="308" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B308" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="309" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B309" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="311" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B311" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="313" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B313" t="s">
+        <v>565</v>
+      </c>
+      <c r="C313" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="314" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B314" t="s">
+        <v>567</v>
+      </c>
+      <c r="C314" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="315" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B315" t="s">
+        <v>569</v>
+      </c>
+      <c r="C315" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="316" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B316" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="317" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B317" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="319" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B319" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="321" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B321" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="322" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B322" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="324" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B324" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="326" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B326" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="328" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B328" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="330" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B330" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="331" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B331" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="333" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B333" t="s">
+        <v>579</v>
+      </c>
+      <c r="C333" t="s">
+        <v>522</v>
+      </c>
+      <c r="D333" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="334" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B334" t="s">
+        <v>581</v>
+      </c>
+      <c r="C334" t="s">
+        <v>582</v>
+      </c>
+      <c r="D334" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="335" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B335" t="s">
+        <v>584</v>
+      </c>
+      <c r="C335" t="s">
+        <v>585</v>
+      </c>
+      <c r="D335" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="336" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B336" t="s">
+        <v>587</v>
+      </c>
+      <c r="C336" t="s">
+        <v>588</v>
+      </c>
+      <c r="D336" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="337" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B337" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="339" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B339" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="341" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B341" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="342" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B342" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="344" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B344" t="s">
+        <v>579</v>
+      </c>
+      <c r="C344" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="345" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B345" t="s">
+        <v>581</v>
+      </c>
+      <c r="C345" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="346" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B346" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="348" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B348" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="349" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B349" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="351" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B351" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="353" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B353" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="354" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B354" t="s">
+        <v>599</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D898888E-831B-43E6-B2FF-CECB618880FC}">
+  <dimension ref="B2:B304"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B20" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B21" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B22" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B23" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B24" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B25" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B26" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B27" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B28" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B29" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B30" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B31" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B32" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B33" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B34" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B35" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B36" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B37" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B38" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B39" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B40" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B41" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B42" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B43" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B44" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B45" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B46" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B47" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B48" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B49" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B50" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B51" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B52" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B53" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B54" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B55" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B56" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B57" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B58" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B59" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B60" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B61" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B62" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B63" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B64" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B65" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B66" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B67" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B68" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B69" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B70" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B71" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B72" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B73" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B74" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B75" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B76" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B77" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B78" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B79" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B80" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B81" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B82" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B83" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B84" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B85" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B86" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B87" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B88" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B89" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B90" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B91" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B92" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B93" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B94" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="95" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B95" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B96" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B97" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B98" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B99" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B100" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B101" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B102" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B103" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B104" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B105" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B106" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B107" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B108" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B109" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B110" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B111" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B112" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B113" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B114" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B115" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B116" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B117" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B118" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B119" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B120" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B121" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B122" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B123" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B124" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B125" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B126" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B127" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B128" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B129" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B130" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B131" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B132" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B133" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B134" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B135" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B136" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B137" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B138" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B139" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B140" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="141" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B141" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B142" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B143" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B144" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B145" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B146" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B147" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="148" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B148" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B149" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B150" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B151" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B152" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B153" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B154" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B155" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B156" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B157" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B158" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B159" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B160" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B161" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B162" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B163" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B164" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B165" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B166" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B167" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B168" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B169" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B170" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B171" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B172" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B173" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B174" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B175" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B176" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B177" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B178" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B179" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B180" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B181" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B182" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B183" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B184" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B185" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B186" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="187" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B187" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B188" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="189" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B189" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B190" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B191" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="192" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B192" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B193" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B194" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B195" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B196" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B197" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="198" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B198" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="199" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B199" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="200" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B200" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="201" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B201" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="202" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B202" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="203" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B203" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="204" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B204" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="205" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B205" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="206" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B206" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="207" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B207" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="208" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B208" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="209" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B209" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="210" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B210" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="211" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B211" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="212" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B212" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="213" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B213" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="214" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B214" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="215" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B215" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="216" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B216" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="217" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B217" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="218" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B218" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="219" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B219" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="220" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B220" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="221" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B221" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="222" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B222" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="223" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B223" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="224" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B224" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="225" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B225" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="226" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B226" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="227" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B227" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="228" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B228" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="229" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B229" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="230" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B230" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="231" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B231" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="232" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B232" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="233" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B233" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="234" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B234" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="235" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B235" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="236" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B236" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="237" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B237" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="238" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B238" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="239" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B239" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="240" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B240" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="241" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B241" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="242" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B242" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="243" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B243" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="244" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B244" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="245" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B245" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="246" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B246" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="247" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B247" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="248" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B248" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="249" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B249" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="250" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B250" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="251" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B251" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="252" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B252" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="253" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B253" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="254" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B254" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="255" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B255" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="256" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B256" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="257" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B257" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="258" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B258" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="259" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B259" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="260" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B260" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="261" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B261" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="262" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B262" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="263" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B263" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="264" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B264" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="265" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B265" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="266" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B266" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="267" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B267" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="268" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B268" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="269" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B269" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="270" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B270" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="271" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B271" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="272" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B272" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="273" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B273" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="274" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B274" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="275" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B275" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="276" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B276" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="277" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B277" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="278" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B278" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="279" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B279" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="280" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B280" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="281" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B281" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="283" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B283" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="285" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B285" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="286" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B286" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="287" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B287" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="288" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B288" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="289" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B289" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="290" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B290" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="291" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B291" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="292" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B292" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="293" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B293" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="294" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B294" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="295" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B295" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="296" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B296" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="297" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B297" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="298" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B298" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="299" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B299" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="300" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B300" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="302" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B302" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="304" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B304" t="s">
+        <v>600</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9498940C-E50D-40AC-A294-658A84D7F9AA}">
+  <dimension ref="B2:B81"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B20" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B21" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B22" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B23" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B24" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B25" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B27" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B28" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B29" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B30" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B31" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B33" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B34" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B36" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B37" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B38" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B39" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B41" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B43" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B44" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B45" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B47" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B48" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B49" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B51" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B52" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B53" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B55" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B56" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B58" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B59" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B60" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B61" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B62" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B63" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B65" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B66" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B67" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B69" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B70" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B72" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B73" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B74" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B75" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B76" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B78" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B79" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B80" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B81" t="s">
+        <v>711</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/HMRC Info.xlsx
+++ b/HMRC Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WCale\Desktop\flonancial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{909DBF0F-58BA-434C-92A2-F197DD5F5481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF66531-6F55-4B23-B68C-1514DDAC8D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{FBE2A083-299E-45AF-96C3-B1141BD30B63}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="3" activeTab="10" xr2:uid="{FBE2A083-299E-45AF-96C3-B1141BD30B63}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,10 @@
     <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
     <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
     <sheet name="Sheet7" sheetId="7" r:id="rId7"/>
+    <sheet name="Flop" sheetId="8" r:id="rId8"/>
+    <sheet name="Sheet8" sheetId="9" r:id="rId9"/>
+    <sheet name="Sheet9" sheetId="10" r:id="rId10"/>
+    <sheet name="Sheet10" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="754">
   <si>
     <t>At a minimum, digital records must include the date, amount, and category of each transaction — income received (sales, rental payments, other receipts) and allowable expenses (supplies, travel, professional fees, repairs). Making Tax Digital</t>
   </si>
@@ -2178,6 +2182,132 @@
   </si>
   <si>
     <t>Your priority actions are: nail the fraud prevention headers, complete Sandbox testing of all required endpoints, prepare for the Production Approvals Checklist, and make sure your data retention and export capabilities are solid. The AI categorisation is the value-add but the compliance infrastructure is what gets you through the door.</t>
+  </si>
+  <si>
+    <t>Turnover</t>
+  </si>
+  <si>
+    <t>Expenses</t>
+  </si>
+  <si>
+    <t>Use formulas to link B1 and B2 to your real income and expense totals — do not type numbers directly.</t>
+  </si>
+  <si>
+    <t>Replace the example formulas above with your own (e.g. =SUM(Sheet1!D:D)).</t>
+  </si>
+  <si>
+    <t>Upload this file to flonancial.co.uk to submit your quarterly update.</t>
+  </si>
+  <si>
+    <t>ONE SPREADSHEET, ALL YEAR</t>
+  </si>
+  <si>
+    <t>Keep adding transactions to this file throughout the tax year (6 April to 5 April).</t>
+  </si>
+  <si>
+    <t>Each time you upload to Flonancial, your year-to-date totals are sent to HMRC.</t>
+  </si>
+  <si>
+    <t>Each submission replaces the previous one — you do not need a separate file each quarter.</t>
+  </si>
+  <si>
+    <t>If you spot a mistake, just correct it in your spreadsheet and upload again next quarter.</t>
+  </si>
+  <si>
+    <t>HMRC will always use the latest figures you submit.</t>
+  </si>
+  <si>
+    <t>QUARTERLY DEADLINES</t>
+  </si>
+  <si>
+    <t>Quarter</t>
+  </si>
+  <si>
+    <t>Period</t>
+  </si>
+  <si>
+    <t>Submit by</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>6 Apr – 5 Jul</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>6 Jul – 5 Oct</t>
+  </si>
+  <si>
+    <t>Q3</t>
+  </si>
+  <si>
+    <t>6 Oct – 5 Jan</t>
+  </si>
+  <si>
+    <t>Q4</t>
+  </si>
+  <si>
+    <t>6 Jan – 5 Apr</t>
+  </si>
+  <si>
+    <t>2026-27 soft landing: no penalty points for late quarterly updates in the first year.</t>
+  </si>
+  <si>
+    <t>WHICH BUSINESS IS THIS FOR?</t>
+  </si>
+  <si>
+    <t>Use one spreadsheet per business:</t>
+  </si>
+  <si>
+    <t>Sole trader — one spreadsheet for your trade.</t>
+  </si>
+  <si>
+    <t>UK landlord — one spreadsheet for ALL your UK properties combined.</t>
+  </si>
+  <si>
+    <t>Sole trader + landlord — use a separate spreadsheet (and separate submission) for each.</t>
+  </si>
+  <si>
+    <t>HMRC treats each income source as a separate business with its own quarterly updates.</t>
+  </si>
+  <si>
+    <t>RECORD KEEPING</t>
+  </si>
+  <si>
+    <t>HMRC requires you to record the date, amount, and category of every business transaction.</t>
+  </si>
+  <si>
+    <t>This spreadsheet is your digital record. Keep it for at least 5 years.</t>
+  </si>
+  <si>
+    <t>Your paper receipts and invoices can stay on paper — you do not need to scan them.</t>
+  </si>
+  <si>
+    <t>Flonancial does not store your transactions. This file is your record.</t>
+  </si>
+  <si>
+    <t>WHAT HMRC RECEIVES</t>
+  </si>
+  <si>
+    <t>Each quarterly update sends just three numbers to HMRC:</t>
+  </si>
+  <si>
+    <t>1. Turnover (your total income)</t>
+  </si>
+  <si>
+    <t>2. Other business income (usually zero — e.g. grants or insurance payouts)</t>
+  </si>
+  <si>
+    <t>3. Expenses (your total allowable expenses as a single figure)</t>
+  </si>
+  <si>
+    <t>HMRC never sees your individual transactions. The detail stays in this spreadsheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> e.g. =SUM(Expenses!C:C)</t>
   </si>
 </sst>
 </file>
@@ -2213,13 +2343,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2605,6 +2736,247 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2960C9C-BB6A-45BA-AC99-9E65DC59D1B4}">
+  <dimension ref="A1:C50"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B1">
+        <v>53000</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>713</v>
+      </c>
+      <c r="B2" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>724</v>
+      </c>
+      <c r="B19" t="s">
+        <v>725</v>
+      </c>
+      <c r="C19" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>727</v>
+      </c>
+      <c r="B20" t="s">
+        <v>728</v>
+      </c>
+      <c r="C20" s="4">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>729</v>
+      </c>
+      <c r="B21" t="s">
+        <v>730</v>
+      </c>
+      <c r="C21" s="4">
+        <v>46333</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>731</v>
+      </c>
+      <c r="B22" t="s">
+        <v>732</v>
+      </c>
+      <c r="C22" s="4">
+        <v>46060</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>733</v>
+      </c>
+      <c r="B23" t="s">
+        <v>734</v>
+      </c>
+      <c r="C23" s="4">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>752</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B5FFC3-52E7-45E6-9AD4-05CC57DA2DDD}">
+  <dimension ref="B2:B3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B2">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B3">
+        <v>4000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD021F67-FCE6-458E-BA86-4D2E0AB02015}">
   <dimension ref="B2:B24"/>
@@ -9220,4 +9592,26 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0428FAD-95BE-4F9C-A98B-2E0D02FD543B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.90625" customWidth="1"/>
+    <col min="2" max="2" width="11.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51F44215-0535-421C-A505-388F1EC58E19}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/HMRC Info.xlsx
+++ b/HMRC Info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WCale\Desktop\flonancial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF66531-6F55-4B23-B68C-1514DDAC8D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD3DCC4C-CE0E-4A8B-8AD3-259C18327B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="3" activeTab="10" xr2:uid="{FBE2A083-299E-45AF-96C3-B1141BD30B63}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="754">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="757">
   <si>
     <t>At a minimum, digital records must include the date, amount, and category of each transaction — income received (sales, rental payments, other receipts) and allowable expenses (supplies, travel, professional fees, repairs). Making Tax Digital</t>
   </si>
@@ -2308,6 +2308,15 @@
   </si>
   <si>
     <t xml:space="preserve"> e.g. =SUM(Expenses!C:C)</t>
+  </si>
+  <si>
+    <t>Submit SE Q1 (5000 / 1200)</t>
+  </si>
+  <si>
+    <t>Submit SE Q2 (12000 / 3500)</t>
+  </si>
+  <si>
+    <t>Amend SE Q2 (13000 / 4000)</t>
   </si>
 </sst>
 </file>
@@ -2959,17 +2968,50 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B5FFC3-52E7-45E6-9AD4-05CC57DA2DDD}">
-  <dimension ref="B2:B3"/>
+  <dimension ref="A2:D6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>5000</v>
+      </c>
       <c r="B2">
+        <v>12000</v>
+      </c>
+      <c r="C2">
         <v>13000</v>
       </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="D2">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1200</v>
+      </c>
       <c r="B3">
+        <v>3500</v>
+      </c>
+      <c r="C3">
         <v>4000</v>
+      </c>
+      <c r="D3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D4" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D5" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D6" t="s">
+        <v>756</v>
       </c>
     </row>
   </sheetData>
